--- a/research/traditional_assets/database/data/kuwait/kuwait_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_hospitals_healthcare_facilities.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07557774948652066</v>
+        <v>0.07550263286229086</v>
       </c>
       <c r="C2">
-        <v>532.3049960034634</v>
+        <v>527.58919350286</v>
       </c>
       <c r="D2">
-        <v>372.6049960034634</v>
+        <v>373.20639350286</v>
       </c>
       <c r="E2">
-        <v>-8.119999999999999</v>
+        <v>-2.802799999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.317200000000001</v>
       </c>
       <c r="G2">
         <v>159.7</v>
@@ -1451,28 +1451,28 @@
         <v>26.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.26745516</v>
       </c>
       <c r="N2">
-        <v>26.8</v>
+        <v>26.53254484</v>
       </c>
       <c r="O2">
-        <v>4.02</v>
+        <v>3.979881726</v>
       </c>
       <c r="P2">
-        <v>22.78</v>
+        <v>22.552663114</v>
       </c>
       <c r="Q2">
-        <v>29.78</v>
+        <v>29.552663114</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07557774948652066</v>
+        <v>0.07583341703261703</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5697228230745496</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>100.2037126522442</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07550263286229086</v>
+        <v>0.0754275162380611</v>
       </c>
       <c r="C3">
-        <v>527.58919350286</v>
+        <v>522.8753354939427</v>
       </c>
       <c r="D3">
-        <v>373.20639350286</v>
+        <v>373.8097354939427</v>
       </c>
       <c r="E3">
-        <v>-2.802799999999999</v>
+        <v>2.514400000000002</v>
       </c>
       <c r="F3">
-        <v>5.317200000000001</v>
+        <v>10.6344</v>
       </c>
       <c r="G3">
         <v>159.7</v>
@@ -1533,28 +1533,28 @@
         <v>26.8</v>
       </c>
       <c r="M3">
-        <v>0.26745516</v>
+        <v>0.5349103200000001</v>
       </c>
       <c r="N3">
-        <v>26.53254484</v>
+        <v>26.26508968</v>
       </c>
       <c r="O3">
-        <v>3.979881726</v>
+        <v>3.939763452</v>
       </c>
       <c r="P3">
-        <v>22.552663114</v>
+        <v>22.325326228</v>
       </c>
       <c r="Q3">
-        <v>29.552663114</v>
+        <v>29.32532622799999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07583341703261703</v>
+        <v>0.07609430228373582</v>
       </c>
       <c r="T3">
-        <v>0.5697228230745496</v>
+        <v>0.5746717198852082</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>100.2037126522442</v>
+        <v>50.1018563261221</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0754275162380611</v>
+        <v>0.07535239961383131</v>
       </c>
       <c r="C4">
-        <v>522.8753354939427</v>
+        <v>518.1634314226368</v>
       </c>
       <c r="D4">
-        <v>373.8097354939427</v>
+        <v>374.4150314226368</v>
       </c>
       <c r="E4">
-        <v>2.514400000000002</v>
+        <v>7.831600000000002</v>
       </c>
       <c r="F4">
-        <v>10.6344</v>
+        <v>15.9516</v>
       </c>
       <c r="G4">
         <v>159.7</v>
@@ -1615,28 +1615,28 @@
         <v>26.8</v>
       </c>
       <c r="M4">
-        <v>0.5349103200000001</v>
+        <v>0.80236548</v>
       </c>
       <c r="N4">
-        <v>26.26508968</v>
+        <v>25.99763452</v>
       </c>
       <c r="O4">
-        <v>3.939763452</v>
+        <v>3.899645178</v>
       </c>
       <c r="P4">
-        <v>22.325326228</v>
+        <v>22.097989342</v>
       </c>
       <c r="Q4">
-        <v>29.32532622799999</v>
+        <v>29.097989342</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07609430228373582</v>
+        <v>0.07636056661219723</v>
       </c>
       <c r="T4">
-        <v>0.5746717198852082</v>
+        <v>0.5797226558053648</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.1018563261221</v>
+        <v>33.40123755074807</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07535239961383131</v>
+        <v>0.07527728298960153</v>
       </c>
       <c r="C5">
-        <v>518.1634314226368</v>
+        <v>513.4534907961479</v>
       </c>
       <c r="D5">
-        <v>374.4150314226368</v>
+        <v>375.022290796148</v>
       </c>
       <c r="E5">
-        <v>7.831600000000002</v>
+        <v>13.1488</v>
       </c>
       <c r="F5">
-        <v>15.9516</v>
+        <v>21.2688</v>
       </c>
       <c r="G5">
         <v>159.7</v>
@@ -1697,28 +1697,28 @@
         <v>26.8</v>
       </c>
       <c r="M5">
-        <v>0.80236548</v>
+        <v>1.06982064</v>
       </c>
       <c r="N5">
-        <v>25.99763452</v>
+        <v>25.73017936</v>
       </c>
       <c r="O5">
-        <v>3.899645178</v>
+        <v>3.859526904</v>
       </c>
       <c r="P5">
-        <v>22.097989342</v>
+        <v>21.870652456</v>
       </c>
       <c r="Q5">
-        <v>29.097989342</v>
+        <v>28.870652456</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07636056661219723</v>
+        <v>0.07663237811416826</v>
       </c>
       <c r="T5">
-        <v>0.5797226558053648</v>
+        <v>0.5848788195571913</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.40123755074807</v>
+        <v>25.05092816306105</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07527728298960153</v>
+        <v>0.07520216636537173</v>
       </c>
       <c r="C6">
-        <v>513.4534907961479</v>
+        <v>508.7455231834608</v>
       </c>
       <c r="D6">
-        <v>375.022290796148</v>
+        <v>375.6315231834608</v>
       </c>
       <c r="E6">
-        <v>13.1488</v>
+        <v>18.466</v>
       </c>
       <c r="F6">
-        <v>21.2688</v>
+        <v>26.586</v>
       </c>
       <c r="G6">
         <v>159.7</v>
@@ -1779,28 +1779,28 @@
         <v>26.8</v>
       </c>
       <c r="M6">
-        <v>1.06982064</v>
+        <v>1.3372758</v>
       </c>
       <c r="N6">
-        <v>25.73017936</v>
+        <v>25.4627242</v>
       </c>
       <c r="O6">
-        <v>3.859526904</v>
+        <v>3.81940863</v>
       </c>
       <c r="P6">
-        <v>21.870652456</v>
+        <v>21.64331557</v>
       </c>
       <c r="Q6">
-        <v>28.870652456</v>
+        <v>28.64331557</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07663237811416826</v>
+        <v>0.07690991196354921</v>
       </c>
       <c r="T6">
-        <v>0.5848788195571913</v>
+        <v>0.5901435341248458</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.05092816306105</v>
+        <v>20.04074253044884</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07520216636537173</v>
+        <v>0.07512704974114198</v>
       </c>
       <c r="C7">
-        <v>508.7455231834608</v>
+        <v>504.039538215841</v>
       </c>
       <c r="D7">
-        <v>375.6315231834608</v>
+        <v>376.242738215841</v>
       </c>
       <c r="E7">
-        <v>18.466</v>
+        <v>23.78320000000001</v>
       </c>
       <c r="F7">
-        <v>26.586</v>
+        <v>31.90320000000001</v>
       </c>
       <c r="G7">
         <v>159.7</v>
@@ -1861,28 +1861,28 @@
         <v>26.8</v>
       </c>
       <c r="M7">
-        <v>1.3372758</v>
+        <v>1.60473096</v>
       </c>
       <c r="N7">
-        <v>25.4627242</v>
+        <v>25.19526904</v>
       </c>
       <c r="O7">
-        <v>3.81940863</v>
+        <v>3.779290356</v>
       </c>
       <c r="P7">
-        <v>21.64331557</v>
+        <v>21.415978684</v>
       </c>
       <c r="Q7">
-        <v>28.64331557</v>
+        <v>28.415978684</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07690991196354921</v>
+        <v>0.07719335078844891</v>
       </c>
       <c r="T7">
-        <v>0.5901435341248458</v>
+        <v>0.5955202638960674</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.04074253044884</v>
+        <v>16.70061877537403</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07512704974114198</v>
+        <v>0.07505193311691219</v>
       </c>
       <c r="C8">
-        <v>504.039538215841</v>
+        <v>499.335545587344</v>
       </c>
       <c r="D8">
-        <v>376.242738215841</v>
+        <v>376.855945587344</v>
       </c>
       <c r="E8">
-        <v>23.7832</v>
+        <v>29.1004</v>
       </c>
       <c r="F8">
-        <v>31.9032</v>
+        <v>37.2204</v>
       </c>
       <c r="G8">
         <v>159.7</v>
@@ -1943,28 +1943,28 @@
         <v>26.8</v>
       </c>
       <c r="M8">
-        <v>1.60473096</v>
+        <v>1.87218612</v>
       </c>
       <c r="N8">
-        <v>25.19526904</v>
+        <v>24.92781388</v>
       </c>
       <c r="O8">
-        <v>3.779290356</v>
+        <v>3.739172082</v>
       </c>
       <c r="P8">
-        <v>21.415978684</v>
+        <v>21.188641798</v>
       </c>
       <c r="Q8">
-        <v>28.415978684</v>
+        <v>28.188641798</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07719335078844891</v>
+        <v>0.07748288507194859</v>
       </c>
       <c r="T8">
-        <v>0.5955202638960674</v>
+        <v>0.6010126222645196</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.70061877537404</v>
+        <v>14.31481609317775</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07505193311691219</v>
+        <v>0.07507881649268242</v>
       </c>
       <c r="C9">
-        <v>499.335545587344</v>
+        <v>493.7986561862123</v>
       </c>
       <c r="D9">
-        <v>376.855945587344</v>
+        <v>376.6362561862123</v>
       </c>
       <c r="E9">
-        <v>29.10040000000001</v>
+        <v>34.41760000000001</v>
       </c>
       <c r="F9">
-        <v>37.22040000000001</v>
+        <v>42.5376</v>
       </c>
       <c r="G9">
         <v>159.7</v>
@@ -2025,45 +2025,45 @@
         <v>26.8</v>
       </c>
       <c r="M9">
-        <v>1.87218612</v>
+        <v>2.20344768</v>
       </c>
       <c r="N9">
-        <v>24.92781388</v>
+        <v>24.59655232</v>
       </c>
       <c r="O9">
-        <v>3.739172082</v>
+        <v>3.689482848</v>
       </c>
       <c r="P9">
-        <v>21.188641798</v>
+        <v>20.907069472</v>
       </c>
       <c r="Q9">
-        <v>28.188641798</v>
+        <v>27.907069472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07748288507194859</v>
+        <v>0.07777871357900262</v>
       </c>
       <c r="T9">
-        <v>0.6010126222645196</v>
+        <v>0.606624379727938</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.15</v>
       </c>
       <c r="W9">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.31481609317775</v>
+        <v>12.16275759268312</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07507881649268242</v>
+        <v>0.07501644986845261</v>
       </c>
       <c r="C10">
-        <v>493.7986561862123</v>
+        <v>488.991505333456</v>
       </c>
       <c r="D10">
-        <v>376.6362561862123</v>
+        <v>377.146305333456</v>
       </c>
       <c r="E10">
-        <v>34.41760000000001</v>
+        <v>39.7348</v>
       </c>
       <c r="F10">
-        <v>42.5376</v>
+        <v>47.8548</v>
       </c>
       <c r="G10">
         <v>159.7</v>
@@ -2107,28 +2107,28 @@
         <v>26.8</v>
       </c>
       <c r="M10">
-        <v>2.20344768</v>
+        <v>2.47887864</v>
       </c>
       <c r="N10">
-        <v>24.59655232</v>
+        <v>24.32112136</v>
       </c>
       <c r="O10">
-        <v>3.689482848</v>
+        <v>3.648168204</v>
       </c>
       <c r="P10">
-        <v>20.907069472</v>
+        <v>20.672953156</v>
       </c>
       <c r="Q10">
-        <v>27.907069472</v>
+        <v>27.67295315599999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07777871357900262</v>
+        <v>0.07808104381148639</v>
       </c>
       <c r="T10">
-        <v>0.606624379727938</v>
+        <v>0.6123594725202229</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.16275759268312</v>
+        <v>10.81134008238499</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07501644986845261</v>
+        <v>0.07509858324422285</v>
       </c>
       <c r="C11">
-        <v>488.991505333456</v>
+        <v>483.0028867633634</v>
       </c>
       <c r="D11">
-        <v>377.146305333456</v>
+        <v>376.4748867633635</v>
       </c>
       <c r="E11">
-        <v>39.7348</v>
+        <v>45.052</v>
       </c>
       <c r="F11">
-        <v>47.8548</v>
+        <v>53.172</v>
       </c>
       <c r="G11">
         <v>159.7</v>
@@ -2189,45 +2189,45 @@
         <v>26.8</v>
       </c>
       <c r="M11">
-        <v>2.47887864</v>
+        <v>2.844702</v>
       </c>
       <c r="N11">
-        <v>24.32112136</v>
+        <v>23.955298</v>
       </c>
       <c r="O11">
-        <v>3.648168204</v>
+        <v>3.5932947</v>
       </c>
       <c r="P11">
-        <v>20.672953156</v>
+        <v>20.3620033</v>
       </c>
       <c r="Q11">
-        <v>27.67295315599999</v>
+        <v>27.36200329999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07808104381148639</v>
+        <v>0.07839009249358095</v>
       </c>
       <c r="T11">
-        <v>0.6123594725202229</v>
+        <v>0.618222011819003</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.15</v>
       </c>
       <c r="W11">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.81134008238499</v>
+        <v>9.421021955902587</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07509858324422285</v>
+        <v>0.07505066661999306</v>
       </c>
       <c r="C12">
-        <v>483.0028867633634</v>
+        <v>478.077101648862</v>
       </c>
       <c r="D12">
-        <v>376.4748867633635</v>
+        <v>376.8663016488621</v>
       </c>
       <c r="E12">
-        <v>45.05200000000001</v>
+        <v>50.36920000000001</v>
       </c>
       <c r="F12">
-        <v>53.172</v>
+        <v>58.4892</v>
       </c>
       <c r="G12">
         <v>159.7</v>
@@ -2271,28 +2271,28 @@
         <v>26.8</v>
       </c>
       <c r="M12">
-        <v>2.844702</v>
+        <v>3.1291722</v>
       </c>
       <c r="N12">
-        <v>23.955298</v>
+        <v>23.6708278</v>
       </c>
       <c r="O12">
-        <v>3.5932947</v>
+        <v>3.55062417</v>
       </c>
       <c r="P12">
-        <v>20.3620033</v>
+        <v>20.12020363</v>
       </c>
       <c r="Q12">
-        <v>27.36200329999999</v>
+        <v>27.12020363</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07839009249358095</v>
+        <v>0.07870608608987985</v>
       </c>
       <c r="T12">
-        <v>0.618222011819003</v>
+        <v>0.6242162935739355</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.421021955902585</v>
+        <v>8.564565414456897</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07505066661999306</v>
+        <v>0.07500274999576328</v>
       </c>
       <c r="C13">
-        <v>478.077101648862</v>
+        <v>473.1521312769591</v>
       </c>
       <c r="D13">
-        <v>376.8663016488621</v>
+        <v>377.2585312769591</v>
       </c>
       <c r="E13">
-        <v>50.36920000000001</v>
+        <v>55.68640000000001</v>
       </c>
       <c r="F13">
-        <v>58.4892</v>
+        <v>63.8064</v>
       </c>
       <c r="G13">
         <v>159.7</v>
@@ -2353,28 +2353,28 @@
         <v>26.8</v>
       </c>
       <c r="M13">
-        <v>3.1291722</v>
+        <v>3.4136424</v>
       </c>
       <c r="N13">
-        <v>23.6708278</v>
+        <v>23.3863576</v>
       </c>
       <c r="O13">
-        <v>3.55062417</v>
+        <v>3.50795364</v>
       </c>
       <c r="P13">
-        <v>20.12020363</v>
+        <v>19.87840396</v>
       </c>
       <c r="Q13">
-        <v>27.12020363</v>
+        <v>26.87840396</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07870608608987985</v>
+        <v>0.07902926135882191</v>
       </c>
       <c r="T13">
-        <v>0.6242162935739355</v>
+        <v>0.6303468090051164</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.564565414456897</v>
+        <v>7.850851629918822</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07500274999576328</v>
+        <v>0.07504323337153349</v>
       </c>
       <c r="C14">
-        <v>473.1521312769591</v>
+        <v>467.5034943049578</v>
       </c>
       <c r="D14">
-        <v>377.2585312769591</v>
+        <v>376.9270943049578</v>
       </c>
       <c r="E14">
-        <v>55.68640000000001</v>
+        <v>61.00360000000001</v>
       </c>
       <c r="F14">
-        <v>63.8064</v>
+        <v>69.12360000000001</v>
       </c>
       <c r="G14">
         <v>159.7</v>
@@ -2435,45 +2435,45 @@
         <v>26.8</v>
       </c>
       <c r="M14">
-        <v>3.4136424</v>
+        <v>3.75341148</v>
       </c>
       <c r="N14">
-        <v>23.3863576</v>
+        <v>23.04658852</v>
       </c>
       <c r="O14">
-        <v>3.50795364</v>
+        <v>3.456988278</v>
       </c>
       <c r="P14">
-        <v>19.87840396</v>
+        <v>19.589600242</v>
       </c>
       <c r="Q14">
-        <v>26.87840396</v>
+        <v>26.589600242</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07902926135882191</v>
+        <v>0.07935986594429137</v>
       </c>
       <c r="T14">
-        <v>0.6303468090051164</v>
+        <v>0.6366182558255198</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.850851629918822</v>
+        <v>7.14017105313484</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07504323337153349</v>
+        <v>0.07500211674730371</v>
       </c>
       <c r="C15">
-        <v>467.5034943049578</v>
+        <v>462.5229203055249</v>
       </c>
       <c r="D15">
-        <v>376.9270943049578</v>
+        <v>377.2637203055249</v>
       </c>
       <c r="E15">
-        <v>61.00360000000001</v>
+        <v>66.32080000000001</v>
       </c>
       <c r="F15">
-        <v>69.12360000000001</v>
+        <v>74.44080000000001</v>
       </c>
       <c r="G15">
         <v>159.7</v>
@@ -2517,28 +2517,28 @@
         <v>26.8</v>
       </c>
       <c r="M15">
-        <v>3.75341148</v>
+        <v>4.042135440000001</v>
       </c>
       <c r="N15">
-        <v>23.04658852</v>
+        <v>22.75786456</v>
       </c>
       <c r="O15">
-        <v>3.456988278</v>
+        <v>3.413679684</v>
       </c>
       <c r="P15">
-        <v>19.589600242</v>
+        <v>19.344184876</v>
       </c>
       <c r="Q15">
-        <v>26.589600242</v>
+        <v>26.344184876</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07935986594429137</v>
+        <v>0.0796981590084927</v>
       </c>
       <c r="T15">
-        <v>0.6366182558255198</v>
+        <v>0.6430355502463977</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.14017105313484</v>
+        <v>6.63015883505378</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07500211674730371</v>
+        <v>0.07496100012307393</v>
       </c>
       <c r="C16">
-        <v>462.5229203055249</v>
+        <v>457.5429481113623</v>
       </c>
       <c r="D16">
-        <v>377.2637203055249</v>
+        <v>377.6009481113624</v>
       </c>
       <c r="E16">
-        <v>66.32080000000001</v>
+        <v>71.63800000000001</v>
       </c>
       <c r="F16">
-        <v>74.44080000000001</v>
+        <v>79.75800000000001</v>
       </c>
       <c r="G16">
         <v>159.7</v>
@@ -2599,28 +2599,28 @@
         <v>26.8</v>
       </c>
       <c r="M16">
-        <v>4.042135440000001</v>
+        <v>4.3308594</v>
       </c>
       <c r="N16">
-        <v>22.75786456</v>
+        <v>22.4691406</v>
       </c>
       <c r="O16">
-        <v>3.413679684</v>
+        <v>3.37037109</v>
       </c>
       <c r="P16">
-        <v>19.344184876</v>
+        <v>19.09876951</v>
       </c>
       <c r="Q16">
-        <v>26.344184876</v>
+        <v>26.09876951</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0796981590084927</v>
+        <v>0.08004441190949874</v>
       </c>
       <c r="T16">
-        <v>0.6430355502463977</v>
+        <v>0.6496038398301198</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.63015883505378</v>
+        <v>6.188148246050194</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07496100012307393</v>
+        <v>0.07505588349884415</v>
       </c>
       <c r="C17">
-        <v>457.5429481113624</v>
+        <v>451.448447231639</v>
       </c>
       <c r="D17">
-        <v>377.6009481113624</v>
+        <v>376.8236472316389</v>
       </c>
       <c r="E17">
-        <v>71.63799999999999</v>
+        <v>76.9552</v>
       </c>
       <c r="F17">
-        <v>79.758</v>
+        <v>85.07520000000001</v>
       </c>
       <c r="G17">
         <v>159.7</v>
@@ -2681,45 +2681,45 @@
         <v>26.8</v>
       </c>
       <c r="M17">
-        <v>4.3308594</v>
+        <v>4.70465856</v>
       </c>
       <c r="N17">
-        <v>22.4691406</v>
+        <v>22.09534144</v>
       </c>
       <c r="O17">
-        <v>3.37037109</v>
+        <v>3.314301216</v>
       </c>
       <c r="P17">
-        <v>19.09876951</v>
+        <v>18.781040224</v>
       </c>
       <c r="Q17">
-        <v>26.09876951</v>
+        <v>25.78104022399999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08004441190949874</v>
+        <v>0.08039890892719542</v>
       </c>
       <c r="T17">
-        <v>0.6496038398301198</v>
+        <v>0.6563285172610736</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.188148246050196</v>
+        <v>5.696481404168042</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07505588349884415</v>
+        <v>0.07502326687461439</v>
       </c>
       <c r="C18">
-        <v>451.448447231639</v>
+        <v>446.3980869920999</v>
       </c>
       <c r="D18">
-        <v>376.8236472316389</v>
+        <v>377.0904869920998</v>
       </c>
       <c r="E18">
-        <v>76.9552</v>
+        <v>82.2724</v>
       </c>
       <c r="F18">
-        <v>85.07520000000001</v>
+        <v>90.39240000000001</v>
       </c>
       <c r="G18">
         <v>159.7</v>
@@ -2763,28 +2763,28 @@
         <v>26.8</v>
       </c>
       <c r="M18">
-        <v>4.70465856</v>
+        <v>4.99869972</v>
       </c>
       <c r="N18">
-        <v>22.09534144</v>
+        <v>21.80130028</v>
       </c>
       <c r="O18">
-        <v>3.314301216</v>
+        <v>3.270195042</v>
       </c>
       <c r="P18">
-        <v>18.781040224</v>
+        <v>18.531105238</v>
       </c>
       <c r="Q18">
-        <v>25.78104022399999</v>
+        <v>25.53110523799999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08039890892719542</v>
+        <v>0.08076194804170407</v>
       </c>
       <c r="T18">
-        <v>0.6563285172610736</v>
+        <v>0.6632152351120502</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.696481404168042</v>
+        <v>5.361394262746392</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07502326687461439</v>
+        <v>0.07499065025038459</v>
       </c>
       <c r="C19">
-        <v>446.3980869920999</v>
+        <v>441.3481049343192</v>
       </c>
       <c r="D19">
-        <v>377.0904869920998</v>
+        <v>377.3577049343192</v>
       </c>
       <c r="E19">
-        <v>82.2724</v>
+        <v>87.58960000000002</v>
       </c>
       <c r="F19">
-        <v>90.39240000000001</v>
+        <v>95.70960000000002</v>
       </c>
       <c r="G19">
         <v>159.7</v>
@@ -2845,28 +2845,28 @@
         <v>26.8</v>
       </c>
       <c r="M19">
-        <v>4.99869972</v>
+        <v>5.292740880000001</v>
       </c>
       <c r="N19">
-        <v>21.80130028</v>
+        <v>21.50725912</v>
       </c>
       <c r="O19">
-        <v>3.270195042</v>
+        <v>3.226088868</v>
       </c>
       <c r="P19">
-        <v>18.531105238</v>
+        <v>18.281170252</v>
       </c>
       <c r="Q19">
-        <v>25.53110523799999</v>
+        <v>25.281170252</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08076194804170407</v>
+        <v>0.08113384176876171</v>
       </c>
       <c r="T19">
-        <v>0.6632152351120502</v>
+        <v>0.6702699216910993</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.361394262746392</v>
+        <v>5.063539025927148</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07499065025038459</v>
+        <v>0.0749580336261548</v>
       </c>
       <c r="C20">
-        <v>441.3481049343192</v>
+        <v>436.2985018628407</v>
       </c>
       <c r="D20">
-        <v>377.3577049343192</v>
+        <v>377.6253018628407</v>
       </c>
       <c r="E20">
-        <v>87.58959999999999</v>
+        <v>92.9068</v>
       </c>
       <c r="F20">
-        <v>95.70959999999999</v>
+        <v>101.0268</v>
       </c>
       <c r="G20">
         <v>159.7</v>
@@ -2927,28 +2927,28 @@
         <v>26.8</v>
       </c>
       <c r="M20">
-        <v>5.29274088</v>
+        <v>5.586782040000001</v>
       </c>
       <c r="N20">
-        <v>21.50725912</v>
+        <v>21.21321796</v>
       </c>
       <c r="O20">
-        <v>3.226088868</v>
+        <v>3.181982694</v>
       </c>
       <c r="P20">
-        <v>18.281170252</v>
+        <v>18.031235266</v>
       </c>
       <c r="Q20">
-        <v>25.281170252</v>
+        <v>25.031235266</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08113384176876171</v>
+        <v>0.08151491805698124</v>
       </c>
       <c r="T20">
-        <v>0.6702699216910993</v>
+        <v>0.6774987980622238</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.063539025927149</v>
+        <v>4.797036971930982</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0749580336261548</v>
+        <v>0.07492541700192504</v>
       </c>
       <c r="C21">
-        <v>436.2985018628407</v>
+        <v>431.2492785844917</v>
       </c>
       <c r="D21">
-        <v>377.6253018628407</v>
+        <v>377.8932785844917</v>
       </c>
       <c r="E21">
-        <v>92.9068</v>
+        <v>98.224</v>
       </c>
       <c r="F21">
-        <v>101.0268</v>
+        <v>106.344</v>
       </c>
       <c r="G21">
         <v>159.7</v>
@@ -3009,28 +3009,28 @@
         <v>26.8</v>
       </c>
       <c r="M21">
-        <v>5.586782040000001</v>
+        <v>5.880823200000001</v>
       </c>
       <c r="N21">
-        <v>21.21321796</v>
+        <v>20.9191768</v>
       </c>
       <c r="O21">
-        <v>3.181982694</v>
+        <v>3.13787652</v>
       </c>
       <c r="P21">
-        <v>18.031235266</v>
+        <v>17.78130028</v>
       </c>
       <c r="Q21">
-        <v>25.031235266</v>
+        <v>24.78130028</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08151491805698124</v>
+        <v>0.08190552125240629</v>
       </c>
       <c r="T21">
-        <v>0.6774987980622238</v>
+        <v>0.6849083963426263</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.797036971930982</v>
+        <v>4.557185123334433</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07492541700192504</v>
+        <v>0.07533905037769525</v>
       </c>
       <c r="C22">
-        <v>431.2492785844917</v>
+        <v>422.5616058604994</v>
       </c>
       <c r="D22">
-        <v>377.8932785844917</v>
+        <v>374.5228058604994</v>
       </c>
       <c r="E22">
-        <v>98.224</v>
+        <v>103.5412</v>
       </c>
       <c r="F22">
-        <v>106.344</v>
+        <v>111.6612</v>
       </c>
       <c r="G22">
         <v>159.7</v>
@@ -3091,45 +3091,45 @@
         <v>26.8</v>
       </c>
       <c r="M22">
-        <v>5.880823200000001</v>
+        <v>6.454017360000002</v>
       </c>
       <c r="N22">
-        <v>20.9191768</v>
+        <v>20.34598264</v>
       </c>
       <c r="O22">
-        <v>3.13787652</v>
+        <v>3.051897396</v>
       </c>
       <c r="P22">
-        <v>17.78130028</v>
+        <v>17.294085244</v>
       </c>
       <c r="Q22">
-        <v>24.78130028</v>
+        <v>24.29408524399999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08190552125240629</v>
+        <v>0.0823060131363231</v>
       </c>
       <c r="T22">
-        <v>0.6849083963426263</v>
+        <v>0.6925055793896215</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.15</v>
       </c>
       <c r="W22">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.557185123334433</v>
+        <v>4.152452419185931</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07533905037769525</v>
+        <v>0.07598218375346548</v>
       </c>
       <c r="C23">
-        <v>422.5616058604994</v>
+        <v>412.1216451799604</v>
       </c>
       <c r="D23">
-        <v>374.5228058604994</v>
+        <v>369.4000451799604</v>
       </c>
       <c r="E23">
-        <v>103.5412</v>
+        <v>108.8584</v>
       </c>
       <c r="F23">
-        <v>111.6612</v>
+        <v>116.9784</v>
       </c>
       <c r="G23">
         <v>159.7</v>
@@ -3173,45 +3173,45 @@
         <v>26.8</v>
       </c>
       <c r="M23">
-        <v>6.454017360000001</v>
+        <v>7.170775920000001</v>
       </c>
       <c r="N23">
-        <v>20.34598264</v>
+        <v>19.62922408</v>
       </c>
       <c r="O23">
-        <v>3.051897396</v>
+        <v>2.944383612</v>
       </c>
       <c r="P23">
-        <v>17.294085244</v>
+        <v>16.684840468</v>
       </c>
       <c r="Q23">
-        <v>24.29408524399999</v>
+        <v>23.684840468</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0823060131363231</v>
+        <v>0.08271677404290445</v>
       </c>
       <c r="T23">
-        <v>0.6925055793896214</v>
+        <v>0.7002975620019242</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.152452419185931</v>
+        <v>3.737391922295628</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07598218375346548</v>
+        <v>0.0760005671292357</v>
       </c>
       <c r="C24">
-        <v>412.1216451799604</v>
+        <v>406.6600751009111</v>
       </c>
       <c r="D24">
-        <v>369.4000451799604</v>
+        <v>369.2556751009111</v>
       </c>
       <c r="E24">
-        <v>108.8584</v>
+        <v>114.1756</v>
       </c>
       <c r="F24">
-        <v>116.9784</v>
+        <v>122.2956</v>
       </c>
       <c r="G24">
         <v>159.7</v>
@@ -3255,28 +3255,28 @@
         <v>26.8</v>
       </c>
       <c r="M24">
-        <v>7.170775920000001</v>
+        <v>7.496720280000001</v>
       </c>
       <c r="N24">
-        <v>19.62922408</v>
+        <v>19.30327972</v>
       </c>
       <c r="O24">
-        <v>2.944383612</v>
+        <v>2.895491958</v>
       </c>
       <c r="P24">
-        <v>16.684840468</v>
+        <v>16.407787762</v>
       </c>
       <c r="Q24">
-        <v>23.684840468</v>
+        <v>23.40778776199999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08271677404290445</v>
+        <v>0.08313820406394246</v>
       </c>
       <c r="T24">
-        <v>0.7002975620019242</v>
+        <v>0.7082919337729878</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.737391922295628</v>
+        <v>3.574896621326253</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0760005671292357</v>
+        <v>0.07659015050500591</v>
       </c>
       <c r="C25">
-        <v>406.6600751009111</v>
+        <v>396.7718074591957</v>
       </c>
       <c r="D25">
-        <v>369.2556751009111</v>
+        <v>364.6846074591956</v>
       </c>
       <c r="E25">
-        <v>114.1756</v>
+        <v>119.4928</v>
       </c>
       <c r="F25">
-        <v>122.2956</v>
+        <v>127.6128</v>
       </c>
       <c r="G25">
         <v>159.7</v>
@@ -3337,45 +3337,45 @@
         <v>26.8</v>
       </c>
       <c r="M25">
-        <v>7.496720280000001</v>
+        <v>8.179980480000001</v>
       </c>
       <c r="N25">
-        <v>19.30327972</v>
+        <v>18.62001952</v>
       </c>
       <c r="O25">
-        <v>2.895491958</v>
+        <v>2.793002928</v>
       </c>
       <c r="P25">
-        <v>16.407787762</v>
+        <v>15.827016592</v>
       </c>
       <c r="Q25">
-        <v>23.40778776199999</v>
+        <v>22.827016592</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08313820406394246</v>
+        <v>0.08357072434869198</v>
       </c>
       <c r="T25">
-        <v>0.7082919337729878</v>
+        <v>0.7164966837485532</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.574896621326253</v>
+        <v>3.276291436822597</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07659015050500591</v>
+        <v>0.07663233388077613</v>
       </c>
       <c r="C26">
-        <v>396.7718074591957</v>
+        <v>391.1318921856721</v>
       </c>
       <c r="D26">
-        <v>364.6846074591956</v>
+        <v>364.3618921856722</v>
       </c>
       <c r="E26">
-        <v>119.4928</v>
+        <v>124.81</v>
       </c>
       <c r="F26">
-        <v>127.6128</v>
+        <v>132.93</v>
       </c>
       <c r="G26">
         <v>159.7</v>
@@ -3419,28 +3419,28 @@
         <v>26.8</v>
       </c>
       <c r="M26">
-        <v>8.179980480000001</v>
+        <v>8.520813</v>
       </c>
       <c r="N26">
-        <v>18.62001952</v>
+        <v>18.279187</v>
       </c>
       <c r="O26">
-        <v>2.793002928</v>
+        <v>2.74187805</v>
       </c>
       <c r="P26">
-        <v>15.827016592</v>
+        <v>15.53730895</v>
       </c>
       <c r="Q26">
-        <v>22.827016592</v>
+        <v>22.53730895</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08357072434869198</v>
+        <v>0.0840147785077015</v>
       </c>
       <c r="T26">
-        <v>0.7164966837485532</v>
+        <v>0.7249202270568004</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.276291436822597</v>
+        <v>3.145239779349693</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07663233388077613</v>
+        <v>0.07667451725654635</v>
       </c>
       <c r="C27">
-        <v>391.1318921856721</v>
+        <v>385.4925475590441</v>
       </c>
       <c r="D27">
-        <v>364.3618921856722</v>
+        <v>364.0397475590441</v>
       </c>
       <c r="E27">
-        <v>124.81</v>
+        <v>130.1272</v>
       </c>
       <c r="F27">
-        <v>132.93</v>
+        <v>138.2472</v>
       </c>
       <c r="G27">
         <v>159.7</v>
@@ -3501,28 +3501,28 @@
         <v>26.8</v>
       </c>
       <c r="M27">
-        <v>8.520813</v>
+        <v>8.861645520000001</v>
       </c>
       <c r="N27">
-        <v>18.279187</v>
+        <v>17.93835448</v>
       </c>
       <c r="O27">
-        <v>2.74187805</v>
+        <v>2.690753172</v>
       </c>
       <c r="P27">
-        <v>15.53730895</v>
+        <v>15.247601308</v>
       </c>
       <c r="Q27">
-        <v>22.53730895</v>
+        <v>22.247601308</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0840147785077015</v>
+        <v>0.08447083413046803</v>
       </c>
       <c r="T27">
-        <v>0.7249202270568004</v>
+        <v>0.7335714336977029</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.145239779349693</v>
+        <v>3.024269018605474</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07667451725654635</v>
+        <v>0.07850680063231658</v>
       </c>
       <c r="C28">
-        <v>385.4925475590441</v>
+        <v>366.7120336679275</v>
       </c>
       <c r="D28">
-        <v>364.0397475590441</v>
+        <v>350.5764336679275</v>
       </c>
       <c r="E28">
-        <v>130.1272</v>
+        <v>135.4444</v>
       </c>
       <c r="F28">
-        <v>138.2472</v>
+        <v>143.5644</v>
       </c>
       <c r="G28">
         <v>159.7</v>
@@ -3583,45 +3583,45 @@
         <v>26.8</v>
       </c>
       <c r="M28">
-        <v>8.861645520000001</v>
+        <v>10.32228036</v>
       </c>
       <c r="N28">
-        <v>17.93835448</v>
+        <v>16.47771964</v>
       </c>
       <c r="O28">
-        <v>2.690753172</v>
+        <v>2.471657946</v>
       </c>
       <c r="P28">
-        <v>15.247601308</v>
+        <v>14.006061694</v>
       </c>
       <c r="Q28">
-        <v>22.247601308</v>
+        <v>21.006061694</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08447083413046803</v>
+        <v>0.08493938442783092</v>
       </c>
       <c r="T28">
-        <v>0.7335714336977029</v>
+        <v>0.7424596596986303</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.15</v>
       </c>
       <c r="W28">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.024269018605474</v>
+        <v>2.596325527434134</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07850680063231658</v>
+        <v>0.07861528400808679</v>
       </c>
       <c r="C29">
-        <v>366.7120336679275</v>
+        <v>360.6288729031396</v>
       </c>
       <c r="D29">
-        <v>350.5764336679275</v>
+        <v>349.8104729031397</v>
       </c>
       <c r="E29">
-        <v>135.4444</v>
+        <v>140.7616</v>
       </c>
       <c r="F29">
-        <v>143.5644</v>
+        <v>148.8816</v>
       </c>
       <c r="G29">
         <v>159.7</v>
@@ -3665,28 +3665,28 @@
         <v>26.8</v>
       </c>
       <c r="M29">
-        <v>10.32228036</v>
+        <v>10.70458704</v>
       </c>
       <c r="N29">
-        <v>16.47771964</v>
+        <v>16.09541296</v>
       </c>
       <c r="O29">
-        <v>2.471657946</v>
+        <v>2.414311944</v>
       </c>
       <c r="P29">
-        <v>14.006061694</v>
+        <v>13.681101016</v>
       </c>
       <c r="Q29">
-        <v>21.006061694</v>
+        <v>20.68110101599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08493938442783092</v>
+        <v>0.08542095001123165</v>
       </c>
       <c r="T29">
-        <v>0.7424596596986303</v>
+        <v>0.75159478086625</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.596325527434134</v>
+        <v>2.503599615740057</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07861528400808679</v>
+        <v>0.07968511738385702</v>
       </c>
       <c r="C30">
-        <v>360.6288729031396</v>
+        <v>347.9334559079904</v>
       </c>
       <c r="D30">
-        <v>349.8104729031397</v>
+        <v>342.4322559079904</v>
       </c>
       <c r="E30">
-        <v>140.7616</v>
+        <v>146.0788</v>
       </c>
       <c r="F30">
-        <v>148.8816</v>
+        <v>154.1988</v>
       </c>
       <c r="G30">
         <v>159.7</v>
@@ -3747,45 +3747,45 @@
         <v>26.8</v>
       </c>
       <c r="M30">
-        <v>10.70458704</v>
+        <v>11.68826904</v>
       </c>
       <c r="N30">
-        <v>16.09541296</v>
+        <v>15.11173096</v>
       </c>
       <c r="O30">
-        <v>2.414311944</v>
+        <v>2.266759644</v>
       </c>
       <c r="P30">
-        <v>13.681101016</v>
+        <v>12.844971316</v>
       </c>
       <c r="Q30">
-        <v>20.68110101599999</v>
+        <v>19.844971316</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08542095001123165</v>
+        <v>0.08591608082233382</v>
       </c>
       <c r="T30">
-        <v>0.75159478086625</v>
+        <v>0.760987229390704</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.503599615740057</v>
+        <v>2.292897255212393</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.079685117383857</v>
+        <v>0.07982675075962722</v>
       </c>
       <c r="C31">
-        <v>347.9334559079904</v>
+        <v>341.6627316638049</v>
       </c>
       <c r="D31">
-        <v>342.4322559079905</v>
+        <v>341.478731663805</v>
       </c>
       <c r="E31">
-        <v>146.0788</v>
+        <v>151.396</v>
       </c>
       <c r="F31">
-        <v>154.1988</v>
+        <v>159.516</v>
       </c>
       <c r="G31">
         <v>159.7</v>
@@ -3829,28 +3829,28 @@
         <v>26.8</v>
       </c>
       <c r="M31">
-        <v>11.68826904</v>
+        <v>12.0913128</v>
       </c>
       <c r="N31">
-        <v>15.11173096</v>
+        <v>14.7086872</v>
       </c>
       <c r="O31">
-        <v>2.266759644</v>
+        <v>2.20630308</v>
       </c>
       <c r="P31">
-        <v>12.844971316</v>
+        <v>12.50238412</v>
       </c>
       <c r="Q31">
-        <v>19.844971316</v>
+        <v>19.50238411999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08591608082233382</v>
+        <v>0.0864253582280389</v>
       </c>
       <c r="T31">
-        <v>0.760987229390704</v>
+        <v>0.7706480335872852</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.292897255212393</v>
+        <v>2.216467346705314</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07982675075962722</v>
+        <v>0.07996838413539743</v>
       </c>
       <c r="C32">
-        <v>341.6627316638049</v>
+        <v>335.3973029707856</v>
       </c>
       <c r="D32">
-        <v>341.478731663805</v>
+        <v>340.5305029707857</v>
       </c>
       <c r="E32">
-        <v>151.396</v>
+        <v>156.7132</v>
       </c>
       <c r="F32">
-        <v>159.516</v>
+        <v>164.8332</v>
       </c>
       <c r="G32">
         <v>159.7</v>
@@ -3911,28 +3911,28 @@
         <v>26.8</v>
       </c>
       <c r="M32">
-        <v>12.0913128</v>
+        <v>12.49435656</v>
       </c>
       <c r="N32">
-        <v>14.7086872</v>
+        <v>14.30564344</v>
       </c>
       <c r="O32">
-        <v>2.20630308</v>
+        <v>2.145846516</v>
       </c>
       <c r="P32">
-        <v>12.50238412</v>
+        <v>12.159796924</v>
       </c>
       <c r="Q32">
-        <v>19.50238411999999</v>
+        <v>19.15979692399999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0864253582280389</v>
+        <v>0.08694939729767745</v>
       </c>
       <c r="T32">
-        <v>0.7706480335872852</v>
+        <v>0.7805888610939122</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.216467346705314</v>
+        <v>2.1449684000374</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07996838413539743</v>
+        <v>0.08011001751116764</v>
       </c>
       <c r="C33">
-        <v>335.3973029707856</v>
+        <v>329.1371258365416</v>
       </c>
       <c r="D33">
-        <v>340.5305029707857</v>
+        <v>339.5875258365416</v>
       </c>
       <c r="E33">
-        <v>156.7132</v>
+        <v>162.0304</v>
       </c>
       <c r="F33">
-        <v>164.8332</v>
+        <v>170.1504</v>
       </c>
       <c r="G33">
         <v>159.7</v>
@@ -3993,28 +3993,28 @@
         <v>26.8</v>
       </c>
       <c r="M33">
-        <v>12.49435656</v>
+        <v>12.89740032</v>
       </c>
       <c r="N33">
-        <v>14.30564344</v>
+        <v>13.90259968</v>
       </c>
       <c r="O33">
-        <v>2.145846516</v>
+        <v>2.085389951999999</v>
       </c>
       <c r="P33">
-        <v>12.159796924</v>
+        <v>11.817209728</v>
       </c>
       <c r="Q33">
-        <v>19.15979692399999</v>
+        <v>18.81720972799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08694939729767745</v>
+        <v>0.08748884928112891</v>
       </c>
       <c r="T33">
-        <v>0.7805888610939122</v>
+        <v>0.7908220658801459</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.1449684000374</v>
+        <v>2.077938137536231</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08011001751116764</v>
+        <v>0.08025165088693788</v>
       </c>
       <c r="C34">
-        <v>329.1371258365416</v>
+        <v>322.8821567546206</v>
       </c>
       <c r="D34">
-        <v>339.5875258365416</v>
+        <v>338.6497567546206</v>
       </c>
       <c r="E34">
-        <v>162.0304</v>
+        <v>167.3476</v>
       </c>
       <c r="F34">
-        <v>170.1504</v>
+        <v>175.4676</v>
       </c>
       <c r="G34">
         <v>159.7</v>
@@ -4075,28 +4075,28 @@
         <v>26.8</v>
       </c>
       <c r="M34">
-        <v>12.89740032</v>
+        <v>13.30044408</v>
       </c>
       <c r="N34">
-        <v>13.90259968</v>
+        <v>13.49955592</v>
       </c>
       <c r="O34">
-        <v>2.085389951999999</v>
+        <v>2.024933388</v>
       </c>
       <c r="P34">
-        <v>11.817209728</v>
+        <v>11.474622532</v>
       </c>
       <c r="Q34">
-        <v>18.81720972799999</v>
+        <v>18.474622532</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08748884928112891</v>
+        <v>0.08804440430886251</v>
       </c>
       <c r="T34">
-        <v>0.7908220658801459</v>
+        <v>0.8013607394659689</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.077938137536231</v>
+        <v>2.014970315186649</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08025165088693788</v>
+        <v>0.08449708426270811</v>
       </c>
       <c r="C35">
-        <v>322.8821567546206</v>
+        <v>291.6760897483841</v>
       </c>
       <c r="D35">
-        <v>338.6497567546206</v>
+        <v>312.7608897483842</v>
       </c>
       <c r="E35">
-        <v>167.3476</v>
+        <v>172.6648</v>
       </c>
       <c r="F35">
-        <v>175.4676</v>
+        <v>180.7848</v>
       </c>
       <c r="G35">
         <v>159.7</v>
@@ -4157,45 +4157,45 @@
         <v>26.8</v>
       </c>
       <c r="M35">
-        <v>13.30044408</v>
+        <v>16.270632</v>
       </c>
       <c r="N35">
-        <v>13.49955592</v>
+        <v>10.529368</v>
       </c>
       <c r="O35">
-        <v>2.024933388</v>
+        <v>1.5794052</v>
       </c>
       <c r="P35">
-        <v>11.474622532</v>
+        <v>8.949962799999998</v>
       </c>
       <c r="Q35">
-        <v>18.474622532</v>
+        <v>15.94996279999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08804440430886251</v>
+        <v>0.08861679433743652</v>
       </c>
       <c r="T35">
-        <v>0.8013607394659689</v>
+        <v>0.8122187667968167</v>
       </c>
       <c r="U35">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V35">
         <v>0.15</v>
       </c>
       <c r="W35">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.014970315186649</v>
+        <v>1.647139459610419</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08449708426270811</v>
+        <v>0.08475941763847832</v>
       </c>
       <c r="C36">
-        <v>291.6760897483841</v>
+        <v>284.8884083543863</v>
       </c>
       <c r="D36">
-        <v>312.7608897483842</v>
+        <v>311.2904083543864</v>
       </c>
       <c r="E36">
-        <v>172.6648</v>
+        <v>177.982</v>
       </c>
       <c r="F36">
-        <v>180.7848</v>
+        <v>186.102</v>
       </c>
       <c r="G36">
         <v>159.7</v>
@@ -4239,28 +4239,28 @@
         <v>26.8</v>
       </c>
       <c r="M36">
-        <v>16.270632</v>
+        <v>16.74918</v>
       </c>
       <c r="N36">
-        <v>10.529368</v>
+        <v>10.05082</v>
       </c>
       <c r="O36">
-        <v>1.5794052</v>
+        <v>1.507623</v>
       </c>
       <c r="P36">
-        <v>8.949962799999998</v>
+        <v>8.543196999999999</v>
       </c>
       <c r="Q36">
-        <v>15.94996279999999</v>
+        <v>15.543197</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08861679433743652</v>
+        <v>0.08920679636688972</v>
       </c>
       <c r="T36">
-        <v>0.8122187667968167</v>
+        <v>0.823410887276306</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.647139459610419</v>
+        <v>1.600078332192979</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08475941763847832</v>
+        <v>0.08502175101424853</v>
       </c>
       <c r="C37">
-        <v>284.8884083543863</v>
+        <v>278.1144895298114</v>
       </c>
       <c r="D37">
-        <v>311.2904083543864</v>
+        <v>309.8336895298115</v>
       </c>
       <c r="E37">
-        <v>177.982</v>
+        <v>183.2992</v>
       </c>
       <c r="F37">
-        <v>186.102</v>
+        <v>191.4192</v>
       </c>
       <c r="G37">
         <v>159.7</v>
@@ -4321,28 +4321,28 @@
         <v>26.8</v>
       </c>
       <c r="M37">
-        <v>16.74918</v>
+        <v>17.227728</v>
       </c>
       <c r="N37">
-        <v>10.05082</v>
+        <v>9.572271999999998</v>
       </c>
       <c r="O37">
-        <v>1.507623</v>
+        <v>1.4358408</v>
       </c>
       <c r="P37">
-        <v>8.543196999999999</v>
+        <v>8.136431199999999</v>
       </c>
       <c r="Q37">
-        <v>15.543197</v>
+        <v>15.1364312</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08920679636688972</v>
+        <v>0.08981523595976335</v>
       </c>
       <c r="T37">
-        <v>0.823410887276306</v>
+        <v>0.8349527615207792</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.600078332192979</v>
+        <v>1.555631711854285</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08502175101424854</v>
+        <v>0.08528408439001876</v>
       </c>
       <c r="C38">
-        <v>278.1144895298114</v>
+        <v>271.3541409640778</v>
       </c>
       <c r="D38">
-        <v>309.8336895298114</v>
+        <v>308.3905409640778</v>
       </c>
       <c r="E38">
-        <v>183.2992</v>
+        <v>188.6164</v>
       </c>
       <c r="F38">
-        <v>191.4192</v>
+        <v>196.7364</v>
       </c>
       <c r="G38">
         <v>159.7</v>
@@ -4403,28 +4403,28 @@
         <v>26.8</v>
       </c>
       <c r="M38">
-        <v>17.227728</v>
+        <v>17.706276</v>
       </c>
       <c r="N38">
-        <v>9.572272000000002</v>
+        <v>9.093724000000002</v>
       </c>
       <c r="O38">
-        <v>1.4358408</v>
+        <v>1.3640586</v>
       </c>
       <c r="P38">
-        <v>8.136431200000001</v>
+        <v>7.729665400000002</v>
       </c>
       <c r="Q38">
-        <v>15.1364312</v>
+        <v>14.7296654</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08981523595976335</v>
+        <v>0.09044299109526788</v>
       </c>
       <c r="T38">
-        <v>0.8349527615207791</v>
+        <v>0.8468610444714262</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.555631711854285</v>
+        <v>1.513587611533899</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08528408439001876</v>
+        <v>0.1048637907603204</v>
       </c>
       <c r="C39">
-        <v>271.3541409640778</v>
+        <v>186.4831606823536</v>
       </c>
       <c r="D39">
-        <v>308.3905409640778</v>
+        <v>228.8367606823536</v>
       </c>
       <c r="E39">
-        <v>188.6164</v>
+        <v>193.9336</v>
       </c>
       <c r="F39">
-        <v>196.7364</v>
+        <v>202.0536</v>
       </c>
       <c r="G39">
         <v>159.7</v>
@@ -4485,45 +4485,45 @@
         <v>26.8</v>
       </c>
       <c r="M39">
-        <v>17.706276</v>
+        <v>29.66146848000001</v>
       </c>
       <c r="N39">
-        <v>9.093724000000002</v>
+        <v>-2.861468480000006</v>
       </c>
       <c r="O39">
-        <v>1.3640586</v>
+        <v>-0.429220272000001</v>
       </c>
       <c r="P39">
-        <v>7.729665400000002</v>
+        <v>-2.432248208000005</v>
       </c>
       <c r="Q39">
-        <v>14.7296654</v>
+        <v>4.567751791999991</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09044299109526788</v>
+        <v>0.09135509819343912</v>
       </c>
       <c r="T39">
-        <v>0.8468610444714262</v>
+        <v>0.8641633790793101</v>
       </c>
       <c r="U39">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.15</v>
+        <v>0.1355293654024778</v>
       </c>
       <c r="W39">
-        <v>0.0765</v>
+        <v>0.1269042891589163</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.513587611533899</v>
+        <v>0.9035291026831856</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1048637907603204</v>
+        <v>0.1058737907603204</v>
       </c>
       <c r="C40">
-        <v>186.4831606823536</v>
+        <v>178.1608547301972</v>
       </c>
       <c r="D40">
-        <v>228.8367606823536</v>
+        <v>225.8316547301973</v>
       </c>
       <c r="E40">
-        <v>193.9336</v>
+        <v>199.2508</v>
       </c>
       <c r="F40">
-        <v>202.0536</v>
+        <v>207.3708</v>
       </c>
       <c r="G40">
         <v>159.7</v>
@@ -4567,37 +4567,37 @@
         <v>26.8</v>
       </c>
       <c r="M40">
-        <v>29.66146848000001</v>
+        <v>30.44203344000001</v>
       </c>
       <c r="N40">
-        <v>-2.861468480000006</v>
+        <v>-3.642033440000006</v>
       </c>
       <c r="O40">
-        <v>-0.429220272000001</v>
+        <v>-0.5463050160000008</v>
       </c>
       <c r="P40">
-        <v>-2.432248208000005</v>
+        <v>-3.095728424000005</v>
       </c>
       <c r="Q40">
-        <v>4.567751791999991</v>
+        <v>3.904271575999991</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09135509819343912</v>
+        <v>0.09210190308185615</v>
       </c>
       <c r="T40">
-        <v>0.8641633790793101</v>
+        <v>0.8783299918511021</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1355293654024778</v>
+        <v>0.132054253469081</v>
       </c>
       <c r="W40">
-        <v>0.1269042891589163</v>
+        <v>0.1274144355907389</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.9035291026831856</v>
+        <v>0.8803616897938732</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1058737907603204</v>
+        <v>0.1068837907603205</v>
       </c>
       <c r="C41">
-        <v>178.1608547301972</v>
+        <v>169.9164524105018</v>
       </c>
       <c r="D41">
-        <v>225.8316547301973</v>
+        <v>222.9044524105018</v>
       </c>
       <c r="E41">
-        <v>199.2508</v>
+        <v>204.568</v>
       </c>
       <c r="F41">
-        <v>207.3708</v>
+        <v>212.688</v>
       </c>
       <c r="G41">
         <v>159.7</v>
@@ -4649,37 +4649,37 @@
         <v>26.8</v>
       </c>
       <c r="M41">
-        <v>30.44203344000001</v>
+        <v>31.22259840000001</v>
       </c>
       <c r="N41">
-        <v>-3.642033440000006</v>
+        <v>-4.422598400000005</v>
       </c>
       <c r="O41">
-        <v>-0.5463050160000008</v>
+        <v>-0.6633897600000008</v>
       </c>
       <c r="P41">
-        <v>-3.095728424000005</v>
+        <v>-3.759208640000005</v>
       </c>
       <c r="Q41">
-        <v>3.904271575999991</v>
+        <v>3.240791359999992</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09210190308185615</v>
+        <v>0.09287360146655377</v>
       </c>
       <c r="T41">
-        <v>0.8783299918511021</v>
+        <v>0.8929688250486205</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.132054253469081</v>
+        <v>0.128752897132354</v>
       </c>
       <c r="W41">
-        <v>0.1274144355907389</v>
+        <v>0.1278990747009704</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8803616897938732</v>
+        <v>0.8583526475490264</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1068837907603205</v>
+        <v>0.1078937907603204</v>
       </c>
       <c r="C42">
-        <v>169.9164524105018</v>
+        <v>161.7469631545534</v>
       </c>
       <c r="D42">
-        <v>222.9044524105018</v>
+        <v>220.0521631545535</v>
       </c>
       <c r="E42">
-        <v>204.568</v>
+        <v>209.8852</v>
       </c>
       <c r="F42">
-        <v>212.688</v>
+        <v>218.0052</v>
       </c>
       <c r="G42">
         <v>159.7</v>
@@ -4731,37 +4731,37 @@
         <v>26.8</v>
       </c>
       <c r="M42">
-        <v>31.22259840000001</v>
+        <v>32.00316336000001</v>
       </c>
       <c r="N42">
-        <v>-4.422598400000005</v>
+        <v>-5.203163360000008</v>
       </c>
       <c r="O42">
-        <v>-0.6633897600000008</v>
+        <v>-0.7804745040000013</v>
       </c>
       <c r="P42">
-        <v>-3.759208640000005</v>
+        <v>-4.422688856000007</v>
       </c>
       <c r="Q42">
-        <v>3.240791359999992</v>
+        <v>2.57731114399999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09287360146655377</v>
+        <v>0.09367145911852924</v>
       </c>
       <c r="T42">
-        <v>0.8929688250486205</v>
+        <v>0.9081038898799529</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.128752897132354</v>
+        <v>0.1256125825681502</v>
       </c>
       <c r="W42">
-        <v>0.1278990747009704</v>
+        <v>0.1283600728789956</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8583526475490264</v>
+        <v>0.8374172171210013</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1078937907603204</v>
+        <v>0.1089037907603204</v>
       </c>
       <c r="C43">
-        <v>161.7469631545534</v>
+        <v>153.6495475291823</v>
       </c>
       <c r="D43">
-        <v>220.0521631545535</v>
+        <v>217.2719475291823</v>
       </c>
       <c r="E43">
-        <v>209.8852</v>
+        <v>215.2024</v>
       </c>
       <c r="F43">
-        <v>218.0052</v>
+        <v>223.3224</v>
       </c>
       <c r="G43">
         <v>159.7</v>
@@ -4813,37 +4813,37 @@
         <v>26.8</v>
       </c>
       <c r="M43">
-        <v>32.00316336000001</v>
+        <v>32.78372832000001</v>
       </c>
       <c r="N43">
-        <v>-5.203163360000008</v>
+        <v>-5.983728320000008</v>
       </c>
       <c r="O43">
-        <v>-0.7804745040000013</v>
+        <v>-0.8975592480000012</v>
       </c>
       <c r="P43">
-        <v>-4.422688856000007</v>
+        <v>-5.086169072000007</v>
       </c>
       <c r="Q43">
-        <v>2.57731114399999</v>
+        <v>1.91383092799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09367145911852924</v>
+        <v>0.09449682910333147</v>
       </c>
       <c r="T43">
-        <v>0.9081038898799529</v>
+        <v>0.9237608534985728</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1256125825681502</v>
+        <v>0.122621806792718</v>
       </c>
       <c r="W43">
-        <v>0.1283600728789956</v>
+        <v>0.128799118762829</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8374172171210013</v>
+        <v>0.8174787119514537</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1089037907603204</v>
+        <v>0.1335462100071121</v>
       </c>
       <c r="C44">
-        <v>153.6495475291823</v>
+        <v>97.13765274908897</v>
       </c>
       <c r="D44">
-        <v>217.2719475291823</v>
+        <v>166.077252749089</v>
       </c>
       <c r="E44">
-        <v>215.2024</v>
+        <v>220.5196</v>
       </c>
       <c r="F44">
-        <v>223.3224</v>
+        <v>228.6396</v>
       </c>
       <c r="G44">
         <v>159.7</v>
@@ -4895,45 +4895,45 @@
         <v>26.8</v>
       </c>
       <c r="M44">
-        <v>32.78372832000001</v>
+        <v>45.91083168</v>
       </c>
       <c r="N44">
-        <v>-5.983728320000008</v>
+        <v>-19.11083168</v>
       </c>
       <c r="O44">
-        <v>-0.8975592480000012</v>
+        <v>-2.866624752</v>
       </c>
       <c r="P44">
-        <v>-5.086169072000007</v>
+        <v>-16.244206928</v>
       </c>
       <c r="Q44">
-        <v>1.91383092799999</v>
+        <v>-9.244206928000004</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09449682910333146</v>
+        <v>0.09607470197670868</v>
       </c>
       <c r="T44">
-        <v>0.9237608534985727</v>
+        <v>0.9536925188464397</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.122621806792718</v>
+        <v>0.08756103631534125</v>
       </c>
       <c r="W44">
-        <v>0.128799118762829</v>
+        <v>0.1832177439078795</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8174787119514537</v>
+        <v>0.583740242102275</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1335462100071121</v>
+        <v>0.1350962100071121</v>
       </c>
       <c r="C45">
-        <v>97.13765274908897</v>
+        <v>89.39501306990061</v>
       </c>
       <c r="D45">
-        <v>166.077252749089</v>
+        <v>163.6518130699006</v>
       </c>
       <c r="E45">
-        <v>220.5196</v>
+        <v>225.8368</v>
       </c>
       <c r="F45">
-        <v>228.6396</v>
+        <v>233.9568</v>
       </c>
       <c r="G45">
         <v>159.7</v>
@@ -4977,37 +4977,37 @@
         <v>26.8</v>
       </c>
       <c r="M45">
-        <v>45.91083168</v>
+        <v>46.97852544000001</v>
       </c>
       <c r="N45">
-        <v>-19.11083168</v>
+        <v>-20.17852544</v>
       </c>
       <c r="O45">
-        <v>-2.866624752</v>
+        <v>-3.026778816000001</v>
       </c>
       <c r="P45">
-        <v>-16.244206928</v>
+        <v>-17.151746624</v>
       </c>
       <c r="Q45">
-        <v>-9.244206928000004</v>
+        <v>-10.15174662400001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09607470197670868</v>
+        <v>0.09697246451200706</v>
       </c>
       <c r="T45">
-        <v>0.9536925188464397</v>
+        <v>0.9707227423972691</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08756103631534125</v>
+        <v>0.08557101276271985</v>
       </c>
       <c r="W45">
-        <v>0.1832177439078795</v>
+        <v>0.1836173406372459</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.583740242102275</v>
+        <v>0.5704734184181324</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1350962100071121</v>
+        <v>0.1366462100071121</v>
       </c>
       <c r="C46">
-        <v>89.39501306990061</v>
+        <v>81.72219729147739</v>
       </c>
       <c r="D46">
-        <v>163.6518130699006</v>
+        <v>161.2961972914774</v>
       </c>
       <c r="E46">
-        <v>225.8368</v>
+        <v>231.154</v>
       </c>
       <c r="F46">
-        <v>233.9568</v>
+        <v>239.274</v>
       </c>
       <c r="G46">
         <v>159.7</v>
@@ -5059,37 +5059,37 @@
         <v>26.8</v>
       </c>
       <c r="M46">
-        <v>46.97852544000001</v>
+        <v>48.04621920000001</v>
       </c>
       <c r="N46">
-        <v>-20.17852544</v>
+        <v>-21.24621920000001</v>
       </c>
       <c r="O46">
-        <v>-3.026778816000001</v>
+        <v>-3.186932880000001</v>
       </c>
       <c r="P46">
-        <v>-17.151746624</v>
+        <v>-18.05928632000001</v>
       </c>
       <c r="Q46">
-        <v>-10.15174662400001</v>
+        <v>-11.05928632000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09697246451200706</v>
+        <v>0.09790287295767991</v>
       </c>
       <c r="T46">
-        <v>0.9707227423972691</v>
+        <v>0.9883722468044921</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.08557101276271985</v>
+        <v>0.08366943470132607</v>
       </c>
       <c r="W46">
-        <v>0.1836173406372459</v>
+        <v>0.1839991775119737</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5704734184181324</v>
+        <v>0.5577962313421738</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1366462100071121</v>
+        <v>0.1381962100071121</v>
       </c>
       <c r="C47">
-        <v>81.72219729147739</v>
+        <v>74.1162330477602</v>
       </c>
       <c r="D47">
-        <v>161.2961972914774</v>
+        <v>159.0074330477602</v>
       </c>
       <c r="E47">
-        <v>231.154</v>
+        <v>236.4712</v>
       </c>
       <c r="F47">
-        <v>239.274</v>
+        <v>244.5912</v>
       </c>
       <c r="G47">
         <v>159.7</v>
@@ -5141,37 +5141,37 @@
         <v>26.8</v>
       </c>
       <c r="M47">
-        <v>48.04621920000001</v>
+        <v>49.11391296000001</v>
       </c>
       <c r="N47">
-        <v>-21.24621920000001</v>
+        <v>-22.31391296000001</v>
       </c>
       <c r="O47">
-        <v>-3.186932880000001</v>
+        <v>-3.347086944000001</v>
       </c>
       <c r="P47">
-        <v>-18.05928632000001</v>
+        <v>-18.96682601600001</v>
       </c>
       <c r="Q47">
-        <v>-11.05928632000001</v>
+        <v>-11.96682601600001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09790287295767991</v>
+        <v>0.09886774097541473</v>
       </c>
       <c r="T47">
-        <v>0.9883722468044921</v>
+        <v>1.006675436560131</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08366943470132607</v>
+        <v>0.08185053394694942</v>
       </c>
       <c r="W47">
-        <v>0.1839991775119737</v>
+        <v>0.1843644127834526</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5577962313421738</v>
+        <v>0.5456702263129962</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1381962100071121</v>
+        <v>0.1397462100071122</v>
       </c>
       <c r="C48">
-        <v>74.1162330477602</v>
+        <v>66.57431432160337</v>
       </c>
       <c r="D48">
-        <v>159.0074330477602</v>
+        <v>156.7827143216034</v>
       </c>
       <c r="E48">
-        <v>236.4712</v>
+        <v>241.7884</v>
       </c>
       <c r="F48">
-        <v>244.5912</v>
+        <v>249.9084</v>
       </c>
       <c r="G48">
         <v>159.7</v>
@@ -5223,37 +5223,37 @@
         <v>26.8</v>
       </c>
       <c r="M48">
-        <v>49.11391296000001</v>
+        <v>50.18160672</v>
       </c>
       <c r="N48">
-        <v>-22.31391296000001</v>
+        <v>-23.38160672</v>
       </c>
       <c r="O48">
-        <v>-3.347086944000001</v>
+        <v>-3.507241008000001</v>
       </c>
       <c r="P48">
-        <v>-18.96682601600001</v>
+        <v>-19.874365712</v>
       </c>
       <c r="Q48">
-        <v>-11.96682601600001</v>
+        <v>-12.87436571200001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09886774097541473</v>
+        <v>0.09986901910702634</v>
       </c>
       <c r="T48">
-        <v>1.006675436560131</v>
+        <v>1.025669312721643</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08185053394694942</v>
+        <v>0.0801090332246739</v>
       </c>
       <c r="W48">
-        <v>0.1843644127834526</v>
+        <v>0.1847141061284855</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5456702263129962</v>
+        <v>0.5340602214978261</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1397462100071122</v>
+        <v>0.1412962100071121</v>
       </c>
       <c r="C49">
-        <v>66.57431432160337</v>
+        <v>59.0937899681702</v>
       </c>
       <c r="D49">
-        <v>156.7827143216034</v>
+        <v>154.6193899681703</v>
       </c>
       <c r="E49">
-        <v>241.7884</v>
+        <v>247.1056</v>
       </c>
       <c r="F49">
-        <v>249.9084</v>
+        <v>255.2256</v>
       </c>
       <c r="G49">
         <v>159.7</v>
@@ -5305,37 +5305,37 @@
         <v>26.8</v>
       </c>
       <c r="M49">
-        <v>50.18160672</v>
+        <v>51.24930048000001</v>
       </c>
       <c r="N49">
-        <v>-23.38160672</v>
+        <v>-24.44930048000001</v>
       </c>
       <c r="O49">
-        <v>-3.507241008000001</v>
+        <v>-3.667395072000001</v>
       </c>
       <c r="P49">
-        <v>-19.874365712</v>
+        <v>-20.78190540800001</v>
       </c>
       <c r="Q49">
-        <v>-12.87436571200001</v>
+        <v>-13.78190540800001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09986901910702634</v>
+        <v>0.1009088079360076</v>
       </c>
       <c r="T49">
-        <v>1.025669312721643</v>
+        <v>1.045393722581675</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.0801090332246739</v>
+        <v>0.07844009503249319</v>
       </c>
       <c r="W49">
-        <v>0.1847141061284855</v>
+        <v>0.1850492289174754</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5340602214978261</v>
+        <v>0.522933966883288</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1412962100071121</v>
+        <v>0.1428462100071121</v>
       </c>
       <c r="C50">
-        <v>59.09378996817028</v>
+        <v>51.67215317553661</v>
       </c>
       <c r="D50">
-        <v>154.6193899681703</v>
+        <v>152.5149531755366</v>
       </c>
       <c r="E50">
-        <v>247.1056</v>
+        <v>252.4228</v>
       </c>
       <c r="F50">
-        <v>255.2256</v>
+        <v>260.5428</v>
       </c>
       <c r="G50">
         <v>159.7</v>
@@ -5387,37 +5387,37 @@
         <v>26.8</v>
       </c>
       <c r="M50">
-        <v>51.24930048</v>
+        <v>52.31699424</v>
       </c>
       <c r="N50">
-        <v>-24.44930048</v>
+        <v>-25.51699424</v>
       </c>
       <c r="O50">
-        <v>-3.667395072</v>
+        <v>-3.827549136</v>
       </c>
       <c r="P50">
-        <v>-20.781905408</v>
+        <v>-21.689445104</v>
       </c>
       <c r="Q50">
-        <v>-13.781905408</v>
+        <v>-14.689445104</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1009088079360076</v>
+        <v>0.1019893727974979</v>
       </c>
       <c r="T50">
-        <v>1.045393722581675</v>
+        <v>1.065891638710727</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.0784400950324932</v>
+        <v>0.07683927676652397</v>
       </c>
       <c r="W50">
-        <v>0.1850492289174754</v>
+        <v>0.185370673225282</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5229339668832881</v>
+        <v>0.5122618451101597</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1428462100071121</v>
+        <v>0.1443962100071121</v>
       </c>
       <c r="C51">
-        <v>51.67215317553661</v>
+        <v>44.30703177441319</v>
       </c>
       <c r="D51">
-        <v>152.5149531755366</v>
+        <v>150.4670317744132</v>
       </c>
       <c r="E51">
-        <v>252.4228</v>
+        <v>257.74</v>
       </c>
       <c r="F51">
-        <v>260.5428</v>
+        <v>265.86</v>
       </c>
       <c r="G51">
         <v>159.7</v>
@@ -5469,37 +5469,37 @@
         <v>26.8</v>
       </c>
       <c r="M51">
-        <v>52.31699424</v>
+        <v>53.384688</v>
       </c>
       <c r="N51">
-        <v>-25.51699424</v>
+        <v>-26.584688</v>
       </c>
       <c r="O51">
-        <v>-3.827549136</v>
+        <v>-3.9877032</v>
       </c>
       <c r="P51">
-        <v>-21.689445104</v>
+        <v>-22.5969848</v>
       </c>
       <c r="Q51">
-        <v>-14.689445104</v>
+        <v>-15.5969848</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1019893727974979</v>
+        <v>0.1031131602534479</v>
       </c>
       <c r="T51">
-        <v>1.065891638710727</v>
+        <v>1.087209471484941</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.07683927676652397</v>
+        <v>0.07530249123119348</v>
       </c>
       <c r="W51">
-        <v>0.185370673225282</v>
+        <v>0.1856792597607763</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5122618451101597</v>
+        <v>0.5020166082079565</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1443962100071121</v>
+        <v>0.1639626261546646</v>
       </c>
       <c r="C52">
-        <v>44.30703177441319</v>
+        <v>17.18162194420535</v>
       </c>
       <c r="D52">
-        <v>150.4670317744132</v>
+        <v>128.6588219442054</v>
       </c>
       <c r="E52">
-        <v>257.74</v>
+        <v>263.0572</v>
       </c>
       <c r="F52">
-        <v>265.86</v>
+        <v>271.1772</v>
       </c>
       <c r="G52">
         <v>159.7</v>
@@ -5551,45 +5551,45 @@
         <v>26.8</v>
       </c>
       <c r="M52">
-        <v>53.384688</v>
+        <v>63.94358376000001</v>
       </c>
       <c r="N52">
-        <v>-26.584688</v>
+        <v>-37.14358376000001</v>
       </c>
       <c r="O52">
-        <v>-3.9877032</v>
+        <v>-5.571537564000002</v>
       </c>
       <c r="P52">
-        <v>-22.5969848</v>
+        <v>-31.57204619600001</v>
       </c>
       <c r="Q52">
-        <v>-15.5969848</v>
+        <v>-24.57204619600001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1031131602534479</v>
+        <v>0.1046224413760744</v>
       </c>
       <c r="T52">
-        <v>1.087209471484941</v>
+        <v>1.115839976667288</v>
       </c>
       <c r="U52">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07530249123119348</v>
+        <v>0.06286791830574119</v>
       </c>
       <c r="W52">
-        <v>0.1856792597607763</v>
+        <v>0.2209757448635062</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5020166082079565</v>
+        <v>0.4191194553716079</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1639626261546646</v>
+        <v>0.1658626261546647</v>
       </c>
       <c r="C53">
-        <v>17.18162194420535</v>
+        <v>10.07879449616348</v>
       </c>
       <c r="D53">
-        <v>128.6588219442054</v>
+        <v>126.8731944961635</v>
       </c>
       <c r="E53">
-        <v>263.0572</v>
+        <v>268.3744</v>
       </c>
       <c r="F53">
-        <v>271.1772</v>
+        <v>276.4944</v>
       </c>
       <c r="G53">
         <v>159.7</v>
@@ -5633,37 +5633,37 @@
         <v>26.8</v>
       </c>
       <c r="M53">
-        <v>63.94358376000001</v>
+        <v>65.19737952000001</v>
       </c>
       <c r="N53">
-        <v>-37.14358376000001</v>
+        <v>-38.39737952000002</v>
       </c>
       <c r="O53">
-        <v>-5.571537564000002</v>
+        <v>-5.759606928000002</v>
       </c>
       <c r="P53">
-        <v>-31.57204619600001</v>
+        <v>-32.63777259200001</v>
       </c>
       <c r="Q53">
-        <v>-24.57204619600001</v>
+        <v>-25.63777259200002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1046224413760744</v>
+        <v>0.1058479089047427</v>
       </c>
       <c r="T53">
-        <v>1.115839976667288</v>
+        <v>1.139086642847857</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06286791830574119</v>
+        <v>0.06165891987678463</v>
       </c>
       <c r="W53">
-        <v>0.2209757448635062</v>
+        <v>0.2212608266930542</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4191194553716079</v>
+        <v>0.4110594658452308</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1658626261546647</v>
+        <v>0.1677626261546646</v>
       </c>
       <c r="C54">
-        <v>10.07879449616348</v>
+        <v>3.024853227611118</v>
       </c>
       <c r="D54">
-        <v>126.8731944961635</v>
+        <v>125.1364532276112</v>
       </c>
       <c r="E54">
-        <v>268.3744</v>
+        <v>273.6916000000001</v>
       </c>
       <c r="F54">
-        <v>276.4944</v>
+        <v>281.8116000000001</v>
       </c>
       <c r="G54">
         <v>159.7</v>
@@ -5715,37 +5715,37 @@
         <v>26.8</v>
       </c>
       <c r="M54">
-        <v>65.19737952000001</v>
+        <v>66.45117528000002</v>
       </c>
       <c r="N54">
-        <v>-38.39737952000002</v>
+        <v>-39.65117528000002</v>
       </c>
       <c r="O54">
-        <v>-5.759606928000002</v>
+        <v>-5.947676292000002</v>
       </c>
       <c r="P54">
-        <v>-32.63777259200001</v>
+        <v>-33.70349898800001</v>
       </c>
       <c r="Q54">
-        <v>-25.63777259200002</v>
+        <v>-26.70349898800002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1058479089047427</v>
+        <v>0.1071255239878223</v>
       </c>
       <c r="T54">
-        <v>1.139086642847857</v>
+        <v>1.163322528865896</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06165891987678463</v>
+        <v>0.06049554403005285</v>
       </c>
       <c r="W54">
-        <v>0.2212608266930542</v>
+        <v>0.2215351507177135</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4110594658452308</v>
+        <v>0.4033036268670189</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1677626261546646</v>
+        <v>0.1696626261546647</v>
       </c>
       <c r="C55">
-        <v>3.024853227611118</v>
+        <v>-3.982182330026092</v>
       </c>
       <c r="D55">
-        <v>125.1364532276112</v>
+        <v>123.4466176699739</v>
       </c>
       <c r="E55">
-        <v>273.6916000000001</v>
+        <v>279.0088</v>
       </c>
       <c r="F55">
-        <v>281.8116000000001</v>
+        <v>287.1288</v>
       </c>
       <c r="G55">
         <v>159.7</v>
@@ -5797,37 +5797,37 @@
         <v>26.8</v>
       </c>
       <c r="M55">
-        <v>66.45117528000002</v>
+        <v>67.70497104</v>
       </c>
       <c r="N55">
-        <v>-39.65117528000002</v>
+        <v>-40.90497104000001</v>
       </c>
       <c r="O55">
-        <v>-5.947676292000002</v>
+        <v>-6.135745656000001</v>
       </c>
       <c r="P55">
-        <v>-33.70349898800001</v>
+        <v>-34.76922538400001</v>
       </c>
       <c r="Q55">
-        <v>-26.70349898800002</v>
+        <v>-27.76922538400001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1071255239878223</v>
+        <v>0.108458687552775</v>
       </c>
       <c r="T55">
-        <v>1.163322528865896</v>
+        <v>1.188612149058633</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06049554403005285</v>
+        <v>0.05937525617764447</v>
       </c>
       <c r="W55">
-        <v>0.2215351507177135</v>
+        <v>0.2217993145933114</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4033036268670189</v>
+        <v>0.3958350411842964</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1696626261546647</v>
+        <v>0.1715626261546647</v>
       </c>
       <c r="C56">
-        <v>-3.982182330026092</v>
+        <v>-10.94418709413935</v>
       </c>
       <c r="D56">
-        <v>123.4466176699739</v>
+        <v>121.8018129058607</v>
       </c>
       <c r="E56">
-        <v>279.0088</v>
+        <v>284.326</v>
       </c>
       <c r="F56">
-        <v>287.1288</v>
+        <v>292.446</v>
       </c>
       <c r="G56">
         <v>159.7</v>
@@ -5879,37 +5879,37 @@
         <v>26.8</v>
       </c>
       <c r="M56">
-        <v>67.70497104</v>
+        <v>68.95876680000001</v>
       </c>
       <c r="N56">
-        <v>-40.90497104000001</v>
+        <v>-42.15876680000001</v>
       </c>
       <c r="O56">
-        <v>-6.135745656000001</v>
+        <v>-6.323815020000001</v>
       </c>
       <c r="P56">
-        <v>-34.76922538400001</v>
+        <v>-35.83495178000001</v>
       </c>
       <c r="Q56">
-        <v>-27.76922538400001</v>
+        <v>-28.83495178000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.108458687552775</v>
+        <v>0.1098511028317255</v>
       </c>
       <c r="T56">
-        <v>1.188612149058633</v>
+        <v>1.215025752371047</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05937525617764447</v>
+        <v>0.05829570606532365</v>
       </c>
       <c r="W56">
-        <v>0.2217993145933114</v>
+        <v>0.2220538725097967</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3958350411842964</v>
+        <v>0.388638040435491</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1715626261546647</v>
+        <v>0.1734626261546647</v>
       </c>
       <c r="C57">
-        <v>-10.94418709413935</v>
+        <v>-17.86293737030434</v>
       </c>
       <c r="D57">
-        <v>121.8018129058607</v>
+        <v>120.2002626296957</v>
       </c>
       <c r="E57">
-        <v>284.326</v>
+        <v>289.6432</v>
       </c>
       <c r="F57">
-        <v>292.446</v>
+        <v>297.7632</v>
       </c>
       <c r="G57">
         <v>159.7</v>
@@ -5961,37 +5961,37 @@
         <v>26.8</v>
       </c>
       <c r="M57">
-        <v>68.95876680000001</v>
+        <v>70.21256256000001</v>
       </c>
       <c r="N57">
-        <v>-42.15876680000001</v>
+        <v>-43.41256256000001</v>
       </c>
       <c r="O57">
-        <v>-6.323815020000001</v>
+        <v>-6.511884384000002</v>
       </c>
       <c r="P57">
-        <v>-35.83495178000001</v>
+        <v>-36.90067817600001</v>
       </c>
       <c r="Q57">
-        <v>-28.83495178000002</v>
+        <v>-29.90067817600002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1098511028317255</v>
+        <v>0.1113068097142647</v>
       </c>
       <c r="T57">
-        <v>1.215025752371047</v>
+        <v>1.242639974015843</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05829570606532365</v>
+        <v>0.05725471131415716</v>
       </c>
       <c r="W57">
-        <v>0.2220538725097967</v>
+        <v>0.2222993390721217</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.388638040435491</v>
+        <v>0.3816980754277144</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1734626261546647</v>
+        <v>0.1753626261546647</v>
       </c>
       <c r="C58">
-        <v>-17.86293737030434</v>
+        <v>-24.74011725128815</v>
       </c>
       <c r="D58">
-        <v>120.2002626296957</v>
+        <v>118.6402827487119</v>
       </c>
       <c r="E58">
-        <v>289.6432</v>
+        <v>294.9604</v>
       </c>
       <c r="F58">
-        <v>297.7632</v>
+        <v>303.0804000000001</v>
       </c>
       <c r="G58">
         <v>159.7</v>
@@ -6043,37 +6043,37 @@
         <v>26.8</v>
       </c>
       <c r="M58">
-        <v>70.21256256000001</v>
+        <v>71.46635832000001</v>
       </c>
       <c r="N58">
-        <v>-43.41256256000001</v>
+        <v>-44.66635832000001</v>
       </c>
       <c r="O58">
-        <v>-6.511884384000002</v>
+        <v>-6.699953748000002</v>
       </c>
       <c r="P58">
-        <v>-36.90067817600001</v>
+        <v>-37.96640457200002</v>
       </c>
       <c r="Q58">
-        <v>-29.90067817600002</v>
+        <v>-30.96640457200002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1113068097142647</v>
+        <v>0.1128302238936662</v>
       </c>
       <c r="T58">
-        <v>1.242639974015843</v>
+        <v>1.271538578062724</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05725471131415716</v>
+        <v>0.05625024269461054</v>
       </c>
       <c r="W58">
-        <v>0.2222993390721217</v>
+        <v>0.2225361927726108</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3816980754277144</v>
+        <v>0.3750016179640703</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1753626261546647</v>
+        <v>0.1772626261546647</v>
       </c>
       <c r="C59">
-        <v>-24.74011725128815</v>
+        <v>-31.57732452415468</v>
       </c>
       <c r="D59">
-        <v>118.6402827487119</v>
+        <v>117.1202754758454</v>
       </c>
       <c r="E59">
-        <v>294.9604</v>
+        <v>300.2776000000001</v>
       </c>
       <c r="F59">
-        <v>303.0804000000001</v>
+        <v>308.3976000000001</v>
       </c>
       <c r="G59">
         <v>159.7</v>
@@ -6125,37 +6125,37 @@
         <v>26.8</v>
       </c>
       <c r="M59">
-        <v>71.46635832000001</v>
+        <v>72.72015408000001</v>
       </c>
       <c r="N59">
-        <v>-44.66635832000001</v>
+        <v>-45.92015408000002</v>
       </c>
       <c r="O59">
-        <v>-6.699953748000002</v>
+        <v>-6.888023112000003</v>
       </c>
       <c r="P59">
-        <v>-37.96640457200002</v>
+        <v>-39.03213096800002</v>
       </c>
       <c r="Q59">
-        <v>-30.96640457200002</v>
+        <v>-32.03213096800002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1128302238936662</v>
+        <v>0.1144261816054202</v>
       </c>
       <c r="T59">
-        <v>1.271538578062724</v>
+        <v>1.301813306111836</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05625024269461054</v>
+        <v>0.05528041092401381</v>
       </c>
       <c r="W59">
-        <v>0.2225361927726108</v>
+        <v>0.2227648791041175</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3750016179640703</v>
+        <v>0.3685360728267587</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1772626261546646</v>
+        <v>0.1791626261546646</v>
       </c>
       <c r="C60">
-        <v>-31.57732452415462</v>
+        <v>-38.37607612902707</v>
       </c>
       <c r="D60">
-        <v>117.1202754758454</v>
+        <v>115.638723870973</v>
       </c>
       <c r="E60">
-        <v>300.2776</v>
+        <v>305.5948</v>
       </c>
       <c r="F60">
-        <v>308.3976</v>
+        <v>313.7148</v>
       </c>
       <c r="G60">
         <v>159.7</v>
@@ -6207,37 +6207,37 @@
         <v>26.8</v>
       </c>
       <c r="M60">
-        <v>72.72015408</v>
+        <v>73.97394984</v>
       </c>
       <c r="N60">
-        <v>-45.92015408</v>
+        <v>-47.17394984000001</v>
       </c>
       <c r="O60">
-        <v>-6.888023112</v>
+        <v>-7.076092476</v>
       </c>
       <c r="P60">
-        <v>-39.032130968</v>
+        <v>-40.09785736400001</v>
       </c>
       <c r="Q60">
-        <v>-32.032130968</v>
+        <v>-33.09785736400001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1144261816054202</v>
+        <v>0.1160999909128694</v>
       </c>
       <c r="T60">
-        <v>1.301813306111836</v>
+        <v>1.333564850163344</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05528041092401382</v>
+        <v>0.05434345480665765</v>
       </c>
       <c r="W60">
-        <v>0.2227648791041175</v>
+        <v>0.2229858133565901</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3685360728267587</v>
+        <v>0.362289698711051</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1791626261546646</v>
+        <v>0.1810626261546646</v>
       </c>
       <c r="C61">
-        <v>-38.37607612902707</v>
+        <v>-45.13781320871163</v>
       </c>
       <c r="D61">
-        <v>115.638723870973</v>
+        <v>114.1941867912883</v>
       </c>
       <c r="E61">
-        <v>305.5948</v>
+        <v>310.912</v>
       </c>
       <c r="F61">
-        <v>313.7148</v>
+        <v>319.032</v>
       </c>
       <c r="G61">
         <v>159.7</v>
@@ -6289,37 +6289,37 @@
         <v>26.8</v>
       </c>
       <c r="M61">
-        <v>73.97394984</v>
+        <v>75.22774560000001</v>
       </c>
       <c r="N61">
-        <v>-47.17394984000001</v>
+        <v>-48.42774560000001</v>
       </c>
       <c r="O61">
-        <v>-7.076092476</v>
+        <v>-7.264161840000001</v>
       </c>
       <c r="P61">
-        <v>-40.09785736400001</v>
+        <v>-41.16358376000001</v>
       </c>
       <c r="Q61">
-        <v>-33.09785736400001</v>
+        <v>-34.16358376000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1160999909128694</v>
+        <v>0.1178574906856912</v>
       </c>
       <c r="T61">
-        <v>1.333564850163344</v>
+        <v>1.366903971417427</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05434345480665765</v>
+        <v>0.05343773055988002</v>
       </c>
       <c r="W61">
-        <v>0.2229858133565901</v>
+        <v>0.2231993831339803</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.362289698711051</v>
+        <v>0.3562515370658668</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1810626261546646</v>
+        <v>0.1829626261546646</v>
       </c>
       <c r="C62">
-        <v>-45.13781320871163</v>
+        <v>-51.86390578451699</v>
       </c>
       <c r="D62">
-        <v>114.1941867912883</v>
+        <v>112.785294215483</v>
       </c>
       <c r="E62">
-        <v>310.912</v>
+        <v>316.2292</v>
       </c>
       <c r="F62">
-        <v>319.032</v>
+        <v>324.3492</v>
       </c>
       <c r="G62">
         <v>159.7</v>
@@ -6371,37 +6371,37 @@
         <v>26.8</v>
       </c>
       <c r="M62">
-        <v>75.22774560000001</v>
+        <v>76.48154136000001</v>
       </c>
       <c r="N62">
-        <v>-48.42774560000001</v>
+        <v>-49.68154136000001</v>
       </c>
       <c r="O62">
-        <v>-7.264161840000001</v>
+        <v>-7.452231204000001</v>
       </c>
       <c r="P62">
-        <v>-41.16358376000001</v>
+        <v>-42.22931015600001</v>
       </c>
       <c r="Q62">
-        <v>-34.16358376000001</v>
+        <v>-35.22931015600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1178574906856912</v>
+        <v>0.119705118651991</v>
       </c>
       <c r="T62">
-        <v>1.366903971417427</v>
+        <v>1.401952791197361</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05343773055988002</v>
+        <v>0.05256170219004592</v>
       </c>
       <c r="W62">
-        <v>0.2231993831339803</v>
+        <v>0.2234059506235872</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3562515370658668</v>
+        <v>0.3504113479336394</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1829626261546646</v>
+        <v>0.1848626261546647</v>
       </c>
       <c r="C63">
-        <v>-51.86390578451699</v>
+        <v>-58.55565709015838</v>
       </c>
       <c r="D63">
-        <v>112.785294215483</v>
+        <v>111.4107429098416</v>
       </c>
       <c r="E63">
-        <v>316.2292</v>
+        <v>321.5464</v>
       </c>
       <c r="F63">
-        <v>324.3492</v>
+        <v>329.6664</v>
       </c>
       <c r="G63">
         <v>159.7</v>
@@ -6453,37 +6453,37 @@
         <v>26.8</v>
       </c>
       <c r="M63">
-        <v>76.48154136000001</v>
+        <v>77.73533712000001</v>
       </c>
       <c r="N63">
-        <v>-49.68154136000001</v>
+        <v>-50.93533712000001</v>
       </c>
       <c r="O63">
-        <v>-7.452231204000001</v>
+        <v>-7.640300568000002</v>
       </c>
       <c r="P63">
-        <v>-42.22931015600001</v>
+        <v>-43.29503655200001</v>
       </c>
       <c r="Q63">
-        <v>-35.22931015600001</v>
+        <v>-36.29503655200001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.119705118651991</v>
+        <v>0.1216499901954644</v>
       </c>
       <c r="T63">
-        <v>1.401952791197361</v>
+        <v>1.438846285702555</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05256170219004592</v>
+        <v>0.05171393279988389</v>
       </c>
       <c r="W63">
-        <v>0.2234059506235872</v>
+        <v>0.2236058546457874</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3504113479336394</v>
+        <v>0.3447595519992259</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1848626261546647</v>
+        <v>0.1867626261546647</v>
       </c>
       <c r="C64">
-        <v>-58.55565709015838</v>
+        <v>-65.21430759256702</v>
       </c>
       <c r="D64">
-        <v>111.4107429098416</v>
+        <v>110.069292407433</v>
       </c>
       <c r="E64">
-        <v>321.5464</v>
+        <v>326.8636</v>
       </c>
       <c r="F64">
-        <v>329.6664</v>
+        <v>334.9836</v>
       </c>
       <c r="G64">
         <v>159.7</v>
@@ -6535,37 +6535,37 @@
         <v>26.8</v>
       </c>
       <c r="M64">
-        <v>77.73533712000001</v>
+        <v>78.98913288000001</v>
       </c>
       <c r="N64">
-        <v>-50.93533712000001</v>
+        <v>-52.18913288000002</v>
       </c>
       <c r="O64">
-        <v>-7.640300568000002</v>
+        <v>-7.828369932000002</v>
       </c>
       <c r="P64">
-        <v>-43.29503655200001</v>
+        <v>-44.36076294800002</v>
       </c>
       <c r="Q64">
-        <v>-36.29503655200001</v>
+        <v>-37.36076294800002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1216499901954644</v>
+        <v>0.123699989930477</v>
       </c>
       <c r="T64">
-        <v>1.438846285702555</v>
+        <v>1.477734023153976</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05171393279988389</v>
+        <v>0.05089307672369524</v>
       </c>
       <c r="W64">
-        <v>0.2236058546457874</v>
+        <v>0.2237994125085527</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3447595519992259</v>
+        <v>0.3392871781579683</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1867626261546647</v>
+        <v>0.1886626261546647</v>
       </c>
       <c r="C65">
-        <v>-65.21430759256702</v>
+        <v>-71.84103872567641</v>
       </c>
       <c r="D65">
-        <v>110.069292407433</v>
+        <v>108.7597612743236</v>
       </c>
       <c r="E65">
-        <v>326.8636</v>
+        <v>332.1808</v>
       </c>
       <c r="F65">
-        <v>334.9836</v>
+        <v>340.3008</v>
       </c>
       <c r="G65">
         <v>159.7</v>
@@ -6617,37 +6617,37 @@
         <v>26.8</v>
       </c>
       <c r="M65">
-        <v>78.98913288000001</v>
+        <v>80.24292864000002</v>
       </c>
       <c r="N65">
-        <v>-52.18913288000002</v>
+        <v>-53.44292864000002</v>
       </c>
       <c r="O65">
-        <v>-7.828369932000002</v>
+        <v>-8.016439296000003</v>
       </c>
       <c r="P65">
-        <v>-44.36076294800002</v>
+        <v>-45.42648934400002</v>
       </c>
       <c r="Q65">
-        <v>-37.36076294800002</v>
+        <v>-38.42648934400002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.123699989930477</v>
+        <v>0.1258638785396569</v>
       </c>
       <c r="T65">
-        <v>1.477734023153976</v>
+        <v>1.518782190463808</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05089307672369524</v>
+        <v>0.05009787239988751</v>
       </c>
       <c r="W65">
-        <v>0.2237994125085527</v>
+        <v>0.2239869216881065</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3392871781579683</v>
+        <v>0.33398581599925</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1886626261546647</v>
+        <v>0.1905626261546647</v>
       </c>
       <c r="C66">
-        <v>-71.84103872567641</v>
+        <v>-78.43697636081066</v>
       </c>
       <c r="D66">
-        <v>108.7597612743236</v>
+        <v>107.4810236391894</v>
       </c>
       <c r="E66">
-        <v>332.1808</v>
+        <v>337.498</v>
       </c>
       <c r="F66">
-        <v>340.3008</v>
+        <v>345.6180000000001</v>
       </c>
       <c r="G66">
         <v>159.7</v>
@@ -6699,37 +6699,37 @@
         <v>26.8</v>
       </c>
       <c r="M66">
-        <v>80.24292864000002</v>
+        <v>81.49672440000002</v>
       </c>
       <c r="N66">
-        <v>-53.44292864000002</v>
+        <v>-54.69672440000002</v>
       </c>
       <c r="O66">
-        <v>-8.016439296000003</v>
+        <v>-8.204508660000004</v>
       </c>
       <c r="P66">
-        <v>-45.42648934400002</v>
+        <v>-46.49221574000002</v>
       </c>
       <c r="Q66">
-        <v>-38.42648934400002</v>
+        <v>-39.49221574000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1258638785396569</v>
+        <v>0.1281514179265042</v>
       </c>
       <c r="T66">
-        <v>1.518782190463808</v>
+        <v>1.562175967334203</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05009787239988751</v>
+        <v>0.0493271359014277</v>
       </c>
       <c r="W66">
-        <v>0.2239869216881065</v>
+        <v>0.2241686613544434</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.33398581599925</v>
+        <v>0.3288475726761847</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1905626261546647</v>
+        <v>0.1924626261546646</v>
       </c>
       <c r="C67">
-        <v>-78.43697636081066</v>
+        <v>-85.00319403510002</v>
       </c>
       <c r="D67">
-        <v>107.4810236391894</v>
+        <v>106.2320059649</v>
       </c>
       <c r="E67">
-        <v>337.498</v>
+        <v>342.8152</v>
       </c>
       <c r="F67">
-        <v>345.6180000000001</v>
+        <v>350.9352</v>
       </c>
       <c r="G67">
         <v>159.7</v>
@@ -6781,37 +6781,37 @@
         <v>26.8</v>
       </c>
       <c r="M67">
-        <v>81.49672440000002</v>
+        <v>82.75052016000001</v>
       </c>
       <c r="N67">
-        <v>-54.69672440000002</v>
+        <v>-55.95052016000001</v>
       </c>
       <c r="O67">
-        <v>-8.204508660000004</v>
+        <v>-8.392578024000001</v>
       </c>
       <c r="P67">
-        <v>-46.49221574000002</v>
+        <v>-47.55794213600001</v>
       </c>
       <c r="Q67">
-        <v>-39.49221574000002</v>
+        <v>-40.55794213600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1281514179265042</v>
+        <v>0.1305735184537543</v>
       </c>
       <c r="T67">
-        <v>1.562175967334203</v>
+        <v>1.608122319314621</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0493271359014277</v>
+        <v>0.04857975505443638</v>
       </c>
       <c r="W67">
-        <v>0.2241686613544434</v>
+        <v>0.2243448937581639</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3288475726761847</v>
+        <v>0.3238650336962425</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1924626261546646</v>
+        <v>0.1943626261546647</v>
       </c>
       <c r="C68">
-        <v>-85.00319403510002</v>
+        <v>-91.54071595738122</v>
       </c>
       <c r="D68">
-        <v>106.2320059649</v>
+        <v>105.0116840426188</v>
       </c>
       <c r="E68">
-        <v>342.8152</v>
+        <v>348.1324</v>
       </c>
       <c r="F68">
-        <v>350.9352</v>
+        <v>356.2524</v>
       </c>
       <c r="G68">
         <v>159.7</v>
@@ -6863,37 +6863,37 @@
         <v>26.8</v>
       </c>
       <c r="M68">
-        <v>82.75052016000001</v>
+        <v>84.00431592000001</v>
       </c>
       <c r="N68">
-        <v>-55.95052016000001</v>
+        <v>-57.20431592000001</v>
       </c>
       <c r="O68">
-        <v>-8.392578024000001</v>
+        <v>-8.580647388000001</v>
       </c>
       <c r="P68">
-        <v>-47.55794213600001</v>
+        <v>-48.62366853200001</v>
       </c>
       <c r="Q68">
-        <v>-40.55794213600001</v>
+        <v>-41.62366853200001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1305735184537543</v>
+        <v>0.133142412952353</v>
       </c>
       <c r="T68">
-        <v>1.608122319314621</v>
+        <v>1.656853298687791</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04857975505443638</v>
+        <v>0.04785468408347465</v>
       </c>
       <c r="W68">
-        <v>0.2243448937581639</v>
+        <v>0.2245158654931167</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3238650336962425</v>
+        <v>0.3190312272231642</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1943626261546647</v>
+        <v>0.1962626261546647</v>
       </c>
       <c r="C69">
-        <v>-91.54071595738122</v>
+        <v>-98.05051980927192</v>
       </c>
       <c r="D69">
-        <v>105.0116840426188</v>
+        <v>103.8190801907281</v>
       </c>
       <c r="E69">
-        <v>348.1324</v>
+        <v>353.4496</v>
       </c>
       <c r="F69">
-        <v>356.2524</v>
+        <v>361.5696</v>
       </c>
       <c r="G69">
         <v>159.7</v>
@@ -6945,37 +6945,37 @@
         <v>26.8</v>
       </c>
       <c r="M69">
-        <v>84.00431592000001</v>
+        <v>85.25811168000001</v>
       </c>
       <c r="N69">
-        <v>-57.20431592000001</v>
+        <v>-58.45811168000002</v>
       </c>
       <c r="O69">
-        <v>-8.580647388000001</v>
+        <v>-8.768716752000001</v>
       </c>
       <c r="P69">
-        <v>-48.62366853200001</v>
+        <v>-49.68939492800001</v>
       </c>
       <c r="Q69">
-        <v>-41.62366853200001</v>
+        <v>-42.68939492800001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.133142412952353</v>
+        <v>0.135871863357114</v>
       </c>
       <c r="T69">
-        <v>1.656853298687791</v>
+        <v>1.708629964271785</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04785468408347465</v>
+        <v>0.0471509387293059</v>
       </c>
       <c r="W69">
-        <v>0.2245158654931167</v>
+        <v>0.2246818086476297</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3190312272231642</v>
+        <v>0.3143395915287059</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1962626261546647</v>
+        <v>0.1981626261546647</v>
       </c>
       <c r="C70">
-        <v>-98.05051980927192</v>
+        <v>-104.5335393575203</v>
       </c>
       <c r="D70">
-        <v>103.8190801907281</v>
+        <v>102.6532606424798</v>
       </c>
       <c r="E70">
-        <v>353.4496</v>
+        <v>358.7668</v>
       </c>
       <c r="F70">
-        <v>361.5696</v>
+        <v>366.8868000000001</v>
       </c>
       <c r="G70">
         <v>159.7</v>
@@ -7027,37 +7027,37 @@
         <v>26.8</v>
       </c>
       <c r="M70">
-        <v>85.25811168000001</v>
+        <v>86.51190744000002</v>
       </c>
       <c r="N70">
-        <v>-58.45811168000002</v>
+        <v>-59.71190744000002</v>
       </c>
       <c r="O70">
-        <v>-8.768716752000001</v>
+        <v>-8.956786116000002</v>
       </c>
       <c r="P70">
-        <v>-49.68939492800001</v>
+        <v>-50.75512132400002</v>
       </c>
       <c r="Q70">
-        <v>-42.68939492800001</v>
+        <v>-43.75512132400002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.135871863357114</v>
+        <v>0.1387774073363758</v>
       </c>
       <c r="T70">
-        <v>1.708629964271785</v>
+        <v>1.763747059893455</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0471509387293059</v>
+        <v>0.04646759179120001</v>
       </c>
       <c r="W70">
-        <v>0.2246818086476297</v>
+        <v>0.2248429418556351</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3143395915287059</v>
+        <v>0.3097839452746667</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1981626261546647</v>
+        <v>0.2000626261546647</v>
       </c>
       <c r="C71">
-        <v>-104.5335393575203</v>
+        <v>-110.9906668922989</v>
       </c>
       <c r="D71">
-        <v>102.6532606424798</v>
+        <v>101.5133331077012</v>
       </c>
       <c r="E71">
-        <v>358.7668</v>
+        <v>364.0840000000001</v>
       </c>
       <c r="F71">
-        <v>366.8868000000001</v>
+        <v>372.2040000000001</v>
       </c>
       <c r="G71">
         <v>159.7</v>
@@ -7109,37 +7109,37 @@
         <v>26.8</v>
       </c>
       <c r="M71">
-        <v>86.51190744000002</v>
+        <v>87.76570320000002</v>
       </c>
       <c r="N71">
-        <v>-59.71190744000002</v>
+        <v>-60.96570320000002</v>
       </c>
       <c r="O71">
-        <v>-8.956786116000002</v>
+        <v>-9.144855480000002</v>
       </c>
       <c r="P71">
-        <v>-50.75512132400002</v>
+        <v>-51.82084772000002</v>
       </c>
       <c r="Q71">
-        <v>-43.75512132400002</v>
+        <v>-44.82084772000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1387774073363758</v>
+        <v>0.1418766542475883</v>
       </c>
       <c r="T71">
-        <v>1.763747059893455</v>
+        <v>1.82253862855657</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04646759179120001</v>
+        <v>0.04580376905132572</v>
       </c>
       <c r="W71">
-        <v>0.2248429418556351</v>
+        <v>0.2249994712576974</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3097839452746667</v>
+        <v>0.3053584603421715</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2000626261546647</v>
+        <v>0.2019626261546647</v>
       </c>
       <c r="C72">
-        <v>-110.9906668922989</v>
+        <v>-117.4227555048252</v>
       </c>
       <c r="D72">
-        <v>101.5133331077012</v>
+        <v>100.3984444951749</v>
       </c>
       <c r="E72">
-        <v>364.0840000000001</v>
+        <v>369.4012000000001</v>
       </c>
       <c r="F72">
-        <v>372.2040000000001</v>
+        <v>377.5212000000001</v>
       </c>
       <c r="G72">
         <v>159.7</v>
@@ -7191,37 +7191,37 @@
         <v>26.8</v>
       </c>
       <c r="M72">
-        <v>87.76570320000002</v>
+        <v>89.01949896000002</v>
       </c>
       <c r="N72">
-        <v>-60.96570320000002</v>
+        <v>-62.21949896000002</v>
       </c>
       <c r="O72">
-        <v>-9.144855480000002</v>
+        <v>-9.332924844000003</v>
       </c>
       <c r="P72">
-        <v>-51.82084772000002</v>
+        <v>-52.88657411600002</v>
       </c>
       <c r="Q72">
-        <v>-44.82084772000002</v>
+        <v>-45.88657411600002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1418766542475883</v>
+        <v>0.1451896423250914</v>
       </c>
       <c r="T72">
-        <v>1.82253862855657</v>
+        <v>1.88538478816197</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04580376905132572</v>
+        <v>0.04515864554356058</v>
       </c>
       <c r="W72">
-        <v>0.2249994712576974</v>
+        <v>0.2251515913808284</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3053584603421715</v>
+        <v>0.3010576369570704</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2019626261546646</v>
+        <v>0.2038626261546647</v>
       </c>
       <c r="C73">
-        <v>-117.4227555048251</v>
+        <v>-123.8306212165253</v>
       </c>
       <c r="D73">
-        <v>100.398444495175</v>
+        <v>99.30777878347466</v>
       </c>
       <c r="E73">
-        <v>369.4012</v>
+        <v>374.7184</v>
       </c>
       <c r="F73">
-        <v>377.5212</v>
+        <v>382.8384</v>
       </c>
       <c r="G73">
         <v>159.7</v>
@@ -7273,37 +7273,37 @@
         <v>26.8</v>
       </c>
       <c r="M73">
-        <v>89.01949896000001</v>
+        <v>90.27329472</v>
       </c>
       <c r="N73">
-        <v>-62.21949896000001</v>
+        <v>-63.47329472</v>
       </c>
       <c r="O73">
-        <v>-9.332924844000001</v>
+        <v>-9.520994207999999</v>
       </c>
       <c r="P73">
-        <v>-52.88657411600001</v>
+        <v>-53.952300512</v>
       </c>
       <c r="Q73">
-        <v>-45.88657411600001</v>
+        <v>-46.95230051200001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1451896423250913</v>
+        <v>0.1487392724081303</v>
       </c>
       <c r="T73">
-        <v>1.885384788161969</v>
+        <v>1.952719959167754</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04515864554356058</v>
+        <v>0.04453144213323335</v>
       </c>
       <c r="W73">
-        <v>0.2251515913808284</v>
+        <v>0.2252994859449836</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3010576369570706</v>
+        <v>0.2968762808882224</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2038626261546647</v>
+        <v>0.2057626261546646</v>
       </c>
       <c r="C74">
-        <v>-123.8306212165253</v>
+        <v>-130.215044970911</v>
       </c>
       <c r="D74">
-        <v>99.30777878347466</v>
+        <v>98.24055502908901</v>
       </c>
       <c r="E74">
-        <v>374.7184</v>
+        <v>380.0356</v>
       </c>
       <c r="F74">
-        <v>382.8384</v>
+        <v>388.1556</v>
       </c>
       <c r="G74">
         <v>159.7</v>
@@ -7355,37 +7355,37 @@
         <v>26.8</v>
       </c>
       <c r="M74">
-        <v>90.27329472</v>
+        <v>91.52709048</v>
       </c>
       <c r="N74">
-        <v>-63.47329472</v>
+        <v>-64.72709048</v>
       </c>
       <c r="O74">
-        <v>-9.520994207999999</v>
+        <v>-9.709063572</v>
       </c>
       <c r="P74">
-        <v>-53.952300512</v>
+        <v>-55.018026908</v>
       </c>
       <c r="Q74">
-        <v>-46.95230051200001</v>
+        <v>-48.01802690800001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1487392724081303</v>
+        <v>0.1525518380528758</v>
       </c>
       <c r="T74">
-        <v>1.952719959167754</v>
+        <v>2.025042920618411</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04453144213323335</v>
+        <v>0.04392142237798358</v>
       </c>
       <c r="W74">
-        <v>0.2252994859449836</v>
+        <v>0.2254433286032715</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2968762808882224</v>
+        <v>0.2928094825198905</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2057626261546646</v>
+        <v>0.2076626261546647</v>
       </c>
       <c r="C75">
-        <v>-130.215044970911</v>
+        <v>-136.5767744983851</v>
       </c>
       <c r="D75">
-        <v>98.24055502908901</v>
+        <v>97.19602550161488</v>
       </c>
       <c r="E75">
-        <v>380.0356</v>
+        <v>385.3528</v>
       </c>
       <c r="F75">
-        <v>388.1556</v>
+        <v>393.4728</v>
       </c>
       <c r="G75">
         <v>159.7</v>
@@ -7437,37 +7437,37 @@
         <v>26.8</v>
       </c>
       <c r="M75">
-        <v>91.52709048</v>
+        <v>92.78088624</v>
       </c>
       <c r="N75">
-        <v>-64.72709048</v>
+        <v>-65.98088624</v>
       </c>
       <c r="O75">
-        <v>-9.709063572</v>
+        <v>-9.897132936</v>
       </c>
       <c r="P75">
-        <v>-55.018026908</v>
+        <v>-56.08375330400001</v>
       </c>
       <c r="Q75">
-        <v>-48.01802690800001</v>
+        <v>-49.08375330400001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1525518380528758</v>
+        <v>0.1566576779779864</v>
       </c>
       <c r="T75">
-        <v>2.025042920618411</v>
+        <v>2.102929186796042</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04392142237798358</v>
+        <v>0.04332788964314596</v>
       </c>
       <c r="W75">
-        <v>0.2254433286032715</v>
+        <v>0.2255832836221462</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2928094825198905</v>
+        <v>0.288852597620973</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2076626261546647</v>
+        <v>0.2095626261546647</v>
       </c>
       <c r="C76">
-        <v>-136.5767744983851</v>
+        <v>-142.9165260633357</v>
       </c>
       <c r="D76">
-        <v>97.19602550161488</v>
+        <v>96.17347393666435</v>
       </c>
       <c r="E76">
-        <v>385.3528</v>
+        <v>390.67</v>
       </c>
       <c r="F76">
-        <v>393.4728</v>
+        <v>398.79</v>
       </c>
       <c r="G76">
         <v>159.7</v>
@@ -7519,37 +7519,37 @@
         <v>26.8</v>
       </c>
       <c r="M76">
-        <v>92.78088624</v>
+        <v>94.034682</v>
       </c>
       <c r="N76">
-        <v>-65.98088624</v>
+        <v>-67.23468200000001</v>
       </c>
       <c r="O76">
-        <v>-9.897132936</v>
+        <v>-10.0852023</v>
       </c>
       <c r="P76">
-        <v>-56.08375330400001</v>
+        <v>-57.14947970000001</v>
       </c>
       <c r="Q76">
-        <v>-49.08375330400001</v>
+        <v>-50.14947970000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1566576779779864</v>
+        <v>0.1610919850971059</v>
       </c>
       <c r="T76">
-        <v>2.102929186796042</v>
+        <v>2.187046354267884</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04332788964314596</v>
+        <v>0.04275018444790402</v>
       </c>
       <c r="W76">
-        <v>0.2255832836221462</v>
+        <v>0.2257195065071843</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.288852597620973</v>
+        <v>0.2850012296526934</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2095626261546647</v>
+        <v>0.2114626261546647</v>
       </c>
       <c r="C77">
-        <v>-142.9165260633357</v>
+        <v>-149.2349861020962</v>
       </c>
       <c r="D77">
-        <v>96.17347393666435</v>
+        <v>95.17221389790382</v>
       </c>
       <c r="E77">
-        <v>390.67</v>
+        <v>395.9872</v>
       </c>
       <c r="F77">
-        <v>398.79</v>
+        <v>404.1072</v>
       </c>
       <c r="G77">
         <v>159.7</v>
@@ -7601,37 +7601,37 @@
         <v>26.8</v>
       </c>
       <c r="M77">
-        <v>94.034682</v>
+        <v>95.28847776000001</v>
       </c>
       <c r="N77">
-        <v>-67.23468200000001</v>
+        <v>-68.48847776000001</v>
       </c>
       <c r="O77">
-        <v>-10.0852023</v>
+        <v>-10.273271664</v>
       </c>
       <c r="P77">
-        <v>-57.14947970000001</v>
+        <v>-58.21520609600001</v>
       </c>
       <c r="Q77">
-        <v>-50.14947970000001</v>
+        <v>-51.21520609600002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1610919850971059</v>
+        <v>0.1658958178094853</v>
       </c>
       <c r="T77">
-        <v>2.187046354267884</v>
+        <v>2.278173285695713</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04275018444790402</v>
+        <v>0.04218768202095791</v>
       </c>
       <c r="W77">
-        <v>0.2257195065071843</v>
+        <v>0.2258521445794581</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2850012296526934</v>
+        <v>0.2812512134730527</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2114626261546647</v>
+        <v>0.2133626261546647</v>
       </c>
       <c r="C78">
-        <v>-149.2349861020962</v>
+        <v>-155.5328127596432</v>
       </c>
       <c r="D78">
-        <v>95.17221389790382</v>
+        <v>94.1915872403569</v>
       </c>
       <c r="E78">
-        <v>395.9872</v>
+        <v>401.3044</v>
       </c>
       <c r="F78">
-        <v>404.1072</v>
+        <v>409.4244</v>
       </c>
       <c r="G78">
         <v>159.7</v>
@@ -7683,37 +7683,37 @@
         <v>26.8</v>
       </c>
       <c r="M78">
-        <v>95.28847776000001</v>
+        <v>96.54227352000001</v>
       </c>
       <c r="N78">
-        <v>-68.48847776000001</v>
+        <v>-69.74227352000001</v>
       </c>
       <c r="O78">
-        <v>-10.273271664</v>
+        <v>-10.461341028</v>
       </c>
       <c r="P78">
-        <v>-58.21520609600001</v>
+        <v>-59.28093249200001</v>
       </c>
       <c r="Q78">
-        <v>-51.21520609600002</v>
+        <v>-52.28093249200002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1658958178094853</v>
+        <v>0.1711173751055499</v>
       </c>
       <c r="T78">
-        <v>2.278173285695713</v>
+        <v>2.377224298117266</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04218768202095791</v>
+        <v>0.04163979004665976</v>
       </c>
       <c r="W78">
-        <v>0.2258521445794581</v>
+        <v>0.2259813375069976</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2812512134730527</v>
+        <v>0.277598600311065</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2133626261546647</v>
+        <v>0.2152626261546647</v>
       </c>
       <c r="C79">
-        <v>-155.5328127596432</v>
+        <v>-161.8106373322609</v>
       </c>
       <c r="D79">
-        <v>94.1915872403569</v>
+        <v>93.23096266773923</v>
       </c>
       <c r="E79">
-        <v>401.3044</v>
+        <v>406.6216000000001</v>
       </c>
       <c r="F79">
-        <v>409.4244</v>
+        <v>414.7416000000001</v>
       </c>
       <c r="G79">
         <v>159.7</v>
@@ -7765,37 +7765,37 @@
         <v>26.8</v>
       </c>
       <c r="M79">
-        <v>96.54227352000001</v>
+        <v>97.79606928000001</v>
       </c>
       <c r="N79">
-        <v>-69.74227352000001</v>
+        <v>-70.99606928000001</v>
       </c>
       <c r="O79">
-        <v>-10.461341028</v>
+        <v>-10.649410392</v>
       </c>
       <c r="P79">
-        <v>-59.28093249200001</v>
+        <v>-60.34665888800001</v>
       </c>
       <c r="Q79">
-        <v>-52.28093249200002</v>
+        <v>-53.34665888800002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1711173751055499</v>
+        <v>0.1768136194285295</v>
       </c>
       <c r="T79">
-        <v>2.377224298117266</v>
+        <v>2.485279948031687</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04163979004665976</v>
+        <v>0.04110594658452309</v>
       </c>
       <c r="W79">
-        <v>0.2259813375069976</v>
+        <v>0.2261072177953695</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.277598600311065</v>
+        <v>0.2740396438968206</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2152626261546647</v>
+        <v>0.2171626261546647</v>
       </c>
       <c r="C80">
-        <v>-161.8106373322609</v>
+        <v>-168.0690656228176</v>
       </c>
       <c r="D80">
-        <v>93.23096266773923</v>
+        <v>92.28973437718244</v>
       </c>
       <c r="E80">
-        <v>406.6216000000001</v>
+        <v>411.9388</v>
       </c>
       <c r="F80">
-        <v>414.7416000000001</v>
+        <v>420.0588</v>
       </c>
       <c r="G80">
         <v>159.7</v>
@@ -7847,37 +7847,37 @@
         <v>26.8</v>
       </c>
       <c r="M80">
-        <v>97.79606928000001</v>
+        <v>99.04986504000001</v>
       </c>
       <c r="N80">
-        <v>-70.99606928000001</v>
+        <v>-72.24986504000002</v>
       </c>
       <c r="O80">
-        <v>-10.649410392</v>
+        <v>-10.837479756</v>
       </c>
       <c r="P80">
-        <v>-60.34665888800001</v>
+        <v>-61.41238528400002</v>
       </c>
       <c r="Q80">
-        <v>-53.34665888800002</v>
+        <v>-54.41238528400002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1768136194285295</v>
+        <v>0.1830523632108404</v>
       </c>
       <c r="T80">
-        <v>2.485279948031687</v>
+        <v>2.603626612223672</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04110594658452309</v>
+        <v>0.04058561814674432</v>
       </c>
       <c r="W80">
-        <v>0.2261072177953695</v>
+        <v>0.2262299112409977</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2740396438968206</v>
+        <v>0.2705707876449621</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2171626261546647</v>
+        <v>0.2190626261546647</v>
       </c>
       <c r="C81">
-        <v>-168.0690656228176</v>
+        <v>-174.3086792147691</v>
       </c>
       <c r="D81">
-        <v>92.28973437718244</v>
+        <v>91.36732078523094</v>
       </c>
       <c r="E81">
-        <v>411.9388</v>
+        <v>417.256</v>
       </c>
       <c r="F81">
-        <v>420.0588</v>
+        <v>425.376</v>
       </c>
       <c r="G81">
         <v>159.7</v>
@@ -7929,37 +7929,37 @@
         <v>26.8</v>
       </c>
       <c r="M81">
-        <v>99.04986504000001</v>
+        <v>100.3036608</v>
       </c>
       <c r="N81">
-        <v>-72.24986504000002</v>
+        <v>-73.50366080000002</v>
       </c>
       <c r="O81">
-        <v>-10.837479756</v>
+        <v>-11.02554912</v>
       </c>
       <c r="P81">
-        <v>-61.41238528400002</v>
+        <v>-62.47811168000002</v>
       </c>
       <c r="Q81">
-        <v>-54.41238528400002</v>
+        <v>-55.47811168000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1830523632108404</v>
+        <v>0.1899149813713824</v>
       </c>
       <c r="T81">
-        <v>2.603626612223672</v>
+        <v>2.733807942834855</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04058561814674432</v>
+        <v>0.04007829791991001</v>
       </c>
       <c r="W81">
-        <v>0.2262299112409977</v>
+        <v>0.2263495373504852</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2705707876449621</v>
+        <v>0.2671886527994001</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2190626261546647</v>
+        <v>0.2209626261546647</v>
       </c>
       <c r="C82">
-        <v>-174.3086792147691</v>
+        <v>-180.5300366705161</v>
       </c>
       <c r="D82">
-        <v>91.36732078523094</v>
+        <v>90.46316332948393</v>
       </c>
       <c r="E82">
-        <v>417.256</v>
+        <v>422.5732</v>
       </c>
       <c r="F82">
-        <v>425.376</v>
+        <v>430.6932</v>
       </c>
       <c r="G82">
         <v>159.7</v>
@@ -8011,37 +8011,37 @@
         <v>26.8</v>
       </c>
       <c r="M82">
-        <v>100.3036608</v>
+        <v>101.55745656</v>
       </c>
       <c r="N82">
-        <v>-73.50366080000002</v>
+        <v>-74.75745656000002</v>
       </c>
       <c r="O82">
-        <v>-11.02554912</v>
+        <v>-11.213618484</v>
       </c>
       <c r="P82">
-        <v>-62.47811168000002</v>
+        <v>-63.54383807600002</v>
       </c>
       <c r="Q82">
-        <v>-55.47811168000003</v>
+        <v>-56.54383807600003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1899149813713824</v>
+        <v>0.1974999803909289</v>
       </c>
       <c r="T82">
-        <v>2.733807942834855</v>
+        <v>2.877692571405111</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04007829791991001</v>
+        <v>0.03958350411842964</v>
       </c>
       <c r="W82">
-        <v>0.2263495373504852</v>
+        <v>0.2264662097288743</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2671886527994001</v>
+        <v>0.2638900274561976</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2209626261546647</v>
+        <v>0.2228626261546647</v>
       </c>
       <c r="C83">
-        <v>-180.5300366705161</v>
+        <v>-186.7336746593083</v>
       </c>
       <c r="D83">
-        <v>90.46316332948393</v>
+        <v>89.57672534069172</v>
       </c>
       <c r="E83">
-        <v>422.5732</v>
+        <v>427.8904000000001</v>
       </c>
       <c r="F83">
-        <v>430.6932</v>
+        <v>436.0104000000001</v>
       </c>
       <c r="G83">
         <v>159.7</v>
@@ -8093,37 +8093,37 @@
         <v>26.8</v>
       </c>
       <c r="M83">
-        <v>101.55745656</v>
+        <v>102.81125232</v>
       </c>
       <c r="N83">
-        <v>-74.75745656000002</v>
+        <v>-76.01125232000003</v>
       </c>
       <c r="O83">
-        <v>-11.213618484</v>
+        <v>-11.401687848</v>
       </c>
       <c r="P83">
-        <v>-63.54383807600002</v>
+        <v>-64.60956447200002</v>
       </c>
       <c r="Q83">
-        <v>-56.54383807600003</v>
+        <v>-57.60956447200002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1974999803909289</v>
+        <v>0.2059277570793138</v>
       </c>
       <c r="T83">
-        <v>2.877692571405111</v>
+        <v>3.037564380927618</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03958350411842964</v>
+        <v>0.03910077845844879</v>
       </c>
       <c r="W83">
-        <v>0.2264662097288743</v>
+        <v>0.2265800364394978</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2638900274561976</v>
+        <v>0.2606718563896586</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2228626261546647</v>
+        <v>0.2247626261546647</v>
       </c>
       <c r="C84">
-        <v>-186.7336746593083</v>
+        <v>-192.9201090194774</v>
       </c>
       <c r="D84">
-        <v>89.57672534069172</v>
+        <v>88.70749098052271</v>
       </c>
       <c r="E84">
-        <v>427.8904000000001</v>
+        <v>433.2076000000001</v>
       </c>
       <c r="F84">
-        <v>436.0104000000001</v>
+        <v>441.3276000000001</v>
       </c>
       <c r="G84">
         <v>159.7</v>
@@ -8175,37 +8175,37 @@
         <v>26.8</v>
       </c>
       <c r="M84">
-        <v>102.81125232</v>
+        <v>104.06504808</v>
       </c>
       <c r="N84">
-        <v>-76.01125232000003</v>
+        <v>-77.26504808000003</v>
       </c>
       <c r="O84">
-        <v>-11.401687848</v>
+        <v>-11.589757212</v>
       </c>
       <c r="P84">
-        <v>-64.60956447200002</v>
+        <v>-65.67529086800002</v>
       </c>
       <c r="Q84">
-        <v>-57.60956447200002</v>
+        <v>-58.67529086800002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2059277570793138</v>
+        <v>0.2153470369075088</v>
       </c>
       <c r="T84">
-        <v>3.037564380927618</v>
+        <v>3.216244638629242</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03910077845844879</v>
+        <v>0.03862968474208194</v>
       </c>
       <c r="W84">
-        <v>0.2265800364394978</v>
+        <v>0.2266911203378171</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2606718563896586</v>
+        <v>0.2575312316138796</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2247626261546647</v>
+        <v>0.2266626261546647</v>
       </c>
       <c r="C85">
-        <v>-192.9201090194774</v>
+        <v>-199.0898357594189</v>
       </c>
       <c r="D85">
-        <v>88.70749098052271</v>
+        <v>87.85496424058117</v>
       </c>
       <c r="E85">
-        <v>433.2076000000001</v>
+        <v>438.5248000000001</v>
       </c>
       <c r="F85">
-        <v>441.3276000000001</v>
+        <v>446.6448000000001</v>
       </c>
       <c r="G85">
         <v>159.7</v>
@@ -8257,37 +8257,37 @@
         <v>26.8</v>
       </c>
       <c r="M85">
-        <v>104.06504808</v>
+        <v>105.31884384</v>
       </c>
       <c r="N85">
-        <v>-77.26504808000003</v>
+        <v>-78.51884384000003</v>
       </c>
       <c r="O85">
-        <v>-11.589757212</v>
+        <v>-11.777826576</v>
       </c>
       <c r="P85">
-        <v>-65.67529086800002</v>
+        <v>-66.74101726400002</v>
       </c>
       <c r="Q85">
-        <v>-58.67529086800002</v>
+        <v>-59.74101726400002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2153470369075088</v>
+        <v>0.2259437267142281</v>
       </c>
       <c r="T85">
-        <v>3.216244638629242</v>
+        <v>3.417259928543571</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03862968474208194</v>
+        <v>0.03816980754277144</v>
       </c>
       <c r="W85">
-        <v>0.2266911203378171</v>
+        <v>0.2267995593814145</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2575312316138796</v>
+        <v>0.2544653836184763</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2266626261546646</v>
+        <v>0.2285626261546647</v>
       </c>
       <c r="C86">
-        <v>-199.0898357594189</v>
+        <v>-205.2433320014035</v>
       </c>
       <c r="D86">
-        <v>87.85496424058114</v>
+        <v>87.0186679985965</v>
       </c>
       <c r="E86">
-        <v>438.5248</v>
+        <v>443.842</v>
       </c>
       <c r="F86">
-        <v>446.6448</v>
+        <v>451.962</v>
       </c>
       <c r="G86">
         <v>159.7</v>
@@ -8339,37 +8339,37 @@
         <v>26.8</v>
       </c>
       <c r="M86">
-        <v>105.31884384</v>
+        <v>106.5726396</v>
       </c>
       <c r="N86">
-        <v>-78.51884384000002</v>
+        <v>-79.77263960000001</v>
       </c>
       <c r="O86">
-        <v>-11.777826576</v>
+        <v>-11.96589594</v>
       </c>
       <c r="P86">
-        <v>-66.74101726400002</v>
+        <v>-67.80674366000001</v>
       </c>
       <c r="Q86">
-        <v>-59.74101726400002</v>
+        <v>-60.80674366000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2259437267142279</v>
+        <v>0.2379533084951765</v>
       </c>
       <c r="T86">
-        <v>3.417259928543568</v>
+        <v>3.64507725711314</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03816980754277144</v>
+        <v>0.03772075098344472</v>
       </c>
       <c r="W86">
-        <v>0.2267995593814145</v>
+        <v>0.2269054469181037</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2544653836184763</v>
+        <v>0.2514716732229648</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2285626261546647</v>
+        <v>0.2304626261546647</v>
       </c>
       <c r="C87">
-        <v>-205.2433320014035</v>
+        <v>-211.3810568719914</v>
       </c>
       <c r="D87">
-        <v>87.0186679985965</v>
+        <v>86.1981431280086</v>
       </c>
       <c r="E87">
-        <v>443.842</v>
+        <v>449.1592</v>
       </c>
       <c r="F87">
-        <v>451.962</v>
+        <v>457.2792</v>
       </c>
       <c r="G87">
         <v>159.7</v>
@@ -8421,37 +8421,37 @@
         <v>26.8</v>
       </c>
       <c r="M87">
-        <v>106.5726396</v>
+        <v>107.82643536</v>
       </c>
       <c r="N87">
-        <v>-79.77263960000001</v>
+        <v>-81.02643536000001</v>
       </c>
       <c r="O87">
-        <v>-11.96589594</v>
+        <v>-12.153965304</v>
       </c>
       <c r="P87">
-        <v>-67.80674366000001</v>
+        <v>-68.87247005600001</v>
       </c>
       <c r="Q87">
-        <v>-60.80674366000001</v>
+        <v>-61.87247005600001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2379533084951765</v>
+        <v>0.2516785448162605</v>
       </c>
       <c r="T87">
-        <v>3.64507725711314</v>
+        <v>3.905439918335507</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03772075098344472</v>
+        <v>0.03728213759991629</v>
       </c>
       <c r="W87">
-        <v>0.2269054469181037</v>
+        <v>0.2270088719539398</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2514716732229648</v>
+        <v>0.2485475839994419</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2304626261546647</v>
+        <v>0.2323626261546647</v>
       </c>
       <c r="C88">
-        <v>-211.3810568719914</v>
+        <v>-217.5034523425413</v>
       </c>
       <c r="D88">
-        <v>86.1981431280086</v>
+        <v>85.39294765745872</v>
       </c>
       <c r="E88">
-        <v>449.1592</v>
+        <v>454.4764</v>
       </c>
       <c r="F88">
-        <v>457.2792</v>
+        <v>462.5964</v>
       </c>
       <c r="G88">
         <v>159.7</v>
@@ -8503,37 +8503,37 @@
         <v>26.8</v>
       </c>
       <c r="M88">
-        <v>107.82643536</v>
+        <v>109.08023112</v>
       </c>
       <c r="N88">
-        <v>-81.02643536000001</v>
+        <v>-82.28023112000001</v>
       </c>
       <c r="O88">
-        <v>-12.153965304</v>
+        <v>-12.342034668</v>
       </c>
       <c r="P88">
-        <v>-68.87247005600001</v>
+        <v>-69.93819645200001</v>
       </c>
       <c r="Q88">
-        <v>-61.87247005600001</v>
+        <v>-62.93819645200001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2516785448162605</v>
+        <v>0.2675153559559729</v>
       </c>
       <c r="T88">
-        <v>3.905439918335507</v>
+        <v>4.205858373592084</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03728213759991629</v>
+        <v>0.03685360728267587</v>
       </c>
       <c r="W88">
-        <v>0.2270088719539398</v>
+        <v>0.2271099194027451</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2485475839994419</v>
+        <v>0.2456907152178391</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2323626261546647</v>
+        <v>0.2342626261546647</v>
       </c>
       <c r="C89">
-        <v>-217.5034523425413</v>
+        <v>-223.6109440230474</v>
       </c>
       <c r="D89">
-        <v>85.39294765745872</v>
+        <v>84.60265597695269</v>
       </c>
       <c r="E89">
-        <v>454.4764</v>
+        <v>459.7936</v>
       </c>
       <c r="F89">
-        <v>462.5964</v>
+        <v>467.9136</v>
       </c>
       <c r="G89">
         <v>159.7</v>
@@ -8585,37 +8585,37 @@
         <v>26.8</v>
       </c>
       <c r="M89">
-        <v>109.08023112</v>
+        <v>110.33402688</v>
       </c>
       <c r="N89">
-        <v>-82.28023112000001</v>
+        <v>-83.53402688000001</v>
       </c>
       <c r="O89">
-        <v>-12.342034668</v>
+        <v>-12.530104032</v>
       </c>
       <c r="P89">
-        <v>-69.93819645200001</v>
+        <v>-71.00392284800002</v>
       </c>
       <c r="Q89">
-        <v>-62.93819645200001</v>
+        <v>-64.00392284800002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2675153559559729</v>
+        <v>0.2859916356189707</v>
       </c>
       <c r="T89">
-        <v>4.205858373592084</v>
+        <v>4.556346571391426</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03685360728267587</v>
+        <v>0.03643481629082728</v>
       </c>
       <c r="W89">
-        <v>0.2271099194027451</v>
+        <v>0.2272086703186229</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2456907152178391</v>
+        <v>0.2428987752721818</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2342626261546647</v>
+        <v>0.2361626261546647</v>
       </c>
       <c r="C90">
-        <v>-223.6109440230474</v>
+        <v>-229.7039419122995</v>
       </c>
       <c r="D90">
-        <v>84.60265597695269</v>
+        <v>83.82685808770056</v>
       </c>
       <c r="E90">
-        <v>459.7936</v>
+        <v>465.1108</v>
       </c>
       <c r="F90">
-        <v>467.9136</v>
+        <v>473.2308</v>
       </c>
       <c r="G90">
         <v>159.7</v>
@@ -8667,37 +8667,37 @@
         <v>26.8</v>
       </c>
       <c r="M90">
-        <v>110.33402688</v>
+        <v>111.58782264</v>
       </c>
       <c r="N90">
-        <v>-83.53402688000001</v>
+        <v>-84.78782264000002</v>
       </c>
       <c r="O90">
-        <v>-12.530104032</v>
+        <v>-12.718173396</v>
       </c>
       <c r="P90">
-        <v>-71.00392284800002</v>
+        <v>-72.06964924400002</v>
       </c>
       <c r="Q90">
-        <v>-64.00392284800002</v>
+        <v>-65.06964924400002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2859916356189707</v>
+        <v>0.3078272388570589</v>
       </c>
       <c r="T90">
-        <v>4.556346571391426</v>
+        <v>4.970559896063373</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03643481629082728</v>
+        <v>0.03602543633250338</v>
       </c>
       <c r="W90">
-        <v>0.2272086703186229</v>
+        <v>0.2273052021127957</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2428987752721818</v>
+        <v>0.2401695755500225</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2361626261546647</v>
+        <v>0.2380626261546647</v>
       </c>
       <c r="C91">
-        <v>-229.7039419122995</v>
+        <v>-235.7828411071454</v>
       </c>
       <c r="D91">
-        <v>83.82685808770056</v>
+        <v>83.0651588928547</v>
       </c>
       <c r="E91">
-        <v>465.1108</v>
+        <v>470.4280000000001</v>
       </c>
       <c r="F91">
-        <v>473.2308</v>
+        <v>478.5480000000001</v>
       </c>
       <c r="G91">
         <v>159.7</v>
@@ -8749,37 +8749,37 @@
         <v>26.8</v>
       </c>
       <c r="M91">
-        <v>111.58782264</v>
+        <v>112.8416184</v>
       </c>
       <c r="N91">
-        <v>-84.78782264000002</v>
+        <v>-86.04161840000002</v>
       </c>
       <c r="O91">
-        <v>-12.718173396</v>
+        <v>-12.90624276</v>
       </c>
       <c r="P91">
-        <v>-72.06964924400002</v>
+        <v>-73.13537564000002</v>
       </c>
       <c r="Q91">
-        <v>-65.06964924400002</v>
+        <v>-66.13537564000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3078272388570589</v>
+        <v>0.3340299627427648</v>
       </c>
       <c r="T91">
-        <v>4.970559896063373</v>
+        <v>5.46761588566971</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03602543633250338</v>
+        <v>0.03562515370658668</v>
       </c>
       <c r="W91">
-        <v>0.2273052021127957</v>
+        <v>0.2273995887559869</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2401695755500225</v>
+        <v>0.2375010247105779</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2380626261546647</v>
+        <v>0.2399626261546647</v>
       </c>
       <c r="C92">
-        <v>-235.7828411071454</v>
+        <v>-241.8480224734321</v>
       </c>
       <c r="D92">
-        <v>83.0651588928547</v>
+        <v>82.31717752656792</v>
       </c>
       <c r="E92">
-        <v>470.4280000000001</v>
+        <v>475.7452</v>
       </c>
       <c r="F92">
-        <v>478.5480000000001</v>
+        <v>483.8652</v>
       </c>
       <c r="G92">
         <v>159.7</v>
@@ -8831,37 +8831,37 @@
         <v>26.8</v>
       </c>
       <c r="M92">
-        <v>112.8416184</v>
+        <v>114.09541416</v>
       </c>
       <c r="N92">
-        <v>-86.04161840000002</v>
+        <v>-87.29541416000001</v>
       </c>
       <c r="O92">
-        <v>-12.90624276</v>
+        <v>-13.094312124</v>
       </c>
       <c r="P92">
-        <v>-73.13537564000002</v>
+        <v>-74.20110203600001</v>
       </c>
       <c r="Q92">
-        <v>-66.13537564000002</v>
+        <v>-67.20110203600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3340299627427648</v>
+        <v>0.3660555141586276</v>
       </c>
       <c r="T92">
-        <v>5.46761588566971</v>
+        <v>6.075128761855235</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03562515370658668</v>
+        <v>0.03523366850101979</v>
       </c>
       <c r="W92">
-        <v>0.2273995887559869</v>
+        <v>0.2274919009674595</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2375010247105779</v>
+        <v>0.234891123340132</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2399626261546647</v>
+        <v>0.2418626261546647</v>
       </c>
       <c r="C93">
-        <v>-241.8480224734321</v>
+        <v>-247.8998532810219</v>
       </c>
       <c r="D93">
-        <v>82.31717752656792</v>
+        <v>81.58254671897816</v>
       </c>
       <c r="E93">
-        <v>475.7452</v>
+        <v>481.0624</v>
       </c>
       <c r="F93">
-        <v>483.8652</v>
+        <v>489.1824</v>
       </c>
       <c r="G93">
         <v>159.7</v>
@@ -8913,37 +8913,37 @@
         <v>26.8</v>
       </c>
       <c r="M93">
-        <v>114.09541416</v>
+        <v>115.34920992</v>
       </c>
       <c r="N93">
-        <v>-87.29541416000001</v>
+        <v>-88.54920992000001</v>
       </c>
       <c r="O93">
-        <v>-13.094312124</v>
+        <v>-13.282381488</v>
       </c>
       <c r="P93">
-        <v>-74.20110203600001</v>
+        <v>-75.26682843200001</v>
       </c>
       <c r="Q93">
-        <v>-67.20110203600001</v>
+        <v>-68.26682843200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3660555141586276</v>
+        <v>0.4060874534284561</v>
       </c>
       <c r="T93">
-        <v>6.075128761855235</v>
+        <v>6.834519857087142</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03523366850101979</v>
+        <v>0.03485069384340001</v>
       </c>
       <c r="W93">
-        <v>0.2274919009674595</v>
+        <v>0.2275822063917263</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.234891123340132</v>
+        <v>0.2323379589560001</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2418626261546647</v>
+        <v>0.2437626261546647</v>
       </c>
       <c r="C94">
-        <v>-247.8998532810219</v>
+        <v>-253.9386878051041</v>
       </c>
       <c r="D94">
-        <v>81.58254671897816</v>
+        <v>80.86091219489602</v>
       </c>
       <c r="E94">
-        <v>481.0624</v>
+        <v>486.3796</v>
       </c>
       <c r="F94">
-        <v>489.1824</v>
+        <v>494.4996</v>
       </c>
       <c r="G94">
         <v>159.7</v>
@@ -8995,37 +8995,37 @@
         <v>26.8</v>
       </c>
       <c r="M94">
-        <v>115.34920992</v>
+        <v>116.60300568</v>
       </c>
       <c r="N94">
-        <v>-88.54920992000001</v>
+        <v>-89.80300568000001</v>
       </c>
       <c r="O94">
-        <v>-13.282381488</v>
+        <v>-13.470450852</v>
       </c>
       <c r="P94">
-        <v>-75.26682843200001</v>
+        <v>-76.33255482800001</v>
       </c>
       <c r="Q94">
-        <v>-68.26682843200001</v>
+        <v>-69.33255482800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4060874534284561</v>
+        <v>0.4575570896325213</v>
       </c>
       <c r="T94">
-        <v>6.834519857087142</v>
+        <v>7.810879836671019</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03485069384340001</v>
+        <v>0.03447595519992259</v>
       </c>
       <c r="W94">
-        <v>0.2275822063917263</v>
+        <v>0.2276705697638582</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2323379589560001</v>
+        <v>0.2298397013328173</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2437626261546647</v>
+        <v>0.2456626261546647</v>
       </c>
       <c r="C95">
-        <v>-253.9386878051041</v>
+        <v>-259.964867895876</v>
       </c>
       <c r="D95">
-        <v>80.86091219489602</v>
+        <v>80.15193210412409</v>
       </c>
       <c r="E95">
-        <v>486.3796</v>
+        <v>491.6968000000001</v>
       </c>
       <c r="F95">
-        <v>494.4996</v>
+        <v>499.8168000000001</v>
       </c>
       <c r="G95">
         <v>159.7</v>
@@ -9077,37 +9077,37 @@
         <v>26.8</v>
       </c>
       <c r="M95">
-        <v>116.60300568</v>
+        <v>117.85680144</v>
       </c>
       <c r="N95">
-        <v>-89.80300568000001</v>
+        <v>-91.05680144000002</v>
       </c>
       <c r="O95">
-        <v>-13.470450852</v>
+        <v>-13.658520216</v>
       </c>
       <c r="P95">
-        <v>-76.33255482800001</v>
+        <v>-77.39828122400002</v>
       </c>
       <c r="Q95">
-        <v>-69.33255482800001</v>
+        <v>-70.39828122400002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4575570896325213</v>
+        <v>0.5261832712379417</v>
       </c>
       <c r="T95">
-        <v>7.810879836671019</v>
+        <v>9.112693142782859</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03447595519992259</v>
+        <v>0.03410918971907235</v>
       </c>
       <c r="W95">
-        <v>0.2276705697638582</v>
+        <v>0.2277570530642427</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2298397013328173</v>
+        <v>0.227394598127149</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2456626261546647</v>
+        <v>0.2475626261546647</v>
       </c>
       <c r="C96">
-        <v>-259.964867895876</v>
+        <v>-265.9787235185132</v>
       </c>
       <c r="D96">
-        <v>80.15193210412409</v>
+        <v>79.45527648148686</v>
       </c>
       <c r="E96">
-        <v>491.6968000000001</v>
+        <v>497.0140000000001</v>
       </c>
       <c r="F96">
-        <v>499.8168000000001</v>
+        <v>505.1340000000001</v>
       </c>
       <c r="G96">
         <v>159.7</v>
@@ -9159,37 +9159,37 @@
         <v>26.8</v>
       </c>
       <c r="M96">
-        <v>117.85680144</v>
+        <v>119.1105972</v>
       </c>
       <c r="N96">
-        <v>-91.05680144000002</v>
+        <v>-92.31059720000002</v>
       </c>
       <c r="O96">
-        <v>-13.658520216</v>
+        <v>-13.84658958</v>
       </c>
       <c r="P96">
-        <v>-77.39828122400002</v>
+        <v>-78.46400762000002</v>
       </c>
       <c r="Q96">
-        <v>-70.39828122400002</v>
+        <v>-71.46400762000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5261832712379417</v>
+        <v>0.6222599254855302</v>
       </c>
       <c r="T96">
-        <v>9.112693142782859</v>
+        <v>10.93523177133943</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03410918971907235</v>
+        <v>0.03375014561676633</v>
       </c>
       <c r="W96">
-        <v>0.2277570530642427</v>
+        <v>0.2278417156635665</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.227394598127149</v>
+        <v>0.2250009707784422</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2475626261546647</v>
+        <v>0.2494626261546646</v>
       </c>
       <c r="C97">
-        <v>-265.9787235185132</v>
+        <v>-271.9805732652237</v>
       </c>
       <c r="D97">
-        <v>79.45527648148686</v>
+        <v>78.77062673477636</v>
       </c>
       <c r="E97">
-        <v>497.0140000000001</v>
+        <v>502.3312000000001</v>
       </c>
       <c r="F97">
-        <v>505.1340000000001</v>
+        <v>510.4512000000001</v>
       </c>
       <c r="G97">
         <v>159.7</v>
@@ -9241,37 +9241,37 @@
         <v>26.8</v>
       </c>
       <c r="M97">
-        <v>119.1105972</v>
+        <v>120.36439296</v>
       </c>
       <c r="N97">
-        <v>-92.31059720000002</v>
+        <v>-93.56439296000003</v>
       </c>
       <c r="O97">
-        <v>-13.84658958</v>
+        <v>-14.03465894400001</v>
       </c>
       <c r="P97">
-        <v>-78.46400762000002</v>
+        <v>-79.52973401600003</v>
       </c>
       <c r="Q97">
-        <v>-71.46400762000002</v>
+        <v>-72.52973401600003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6222599254855302</v>
+        <v>0.7663749068569131</v>
       </c>
       <c r="T97">
-        <v>10.93523177133943</v>
+        <v>13.6690397141743</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03375014561676633</v>
+        <v>0.033398581599925</v>
       </c>
       <c r="W97">
-        <v>0.2278417156635665</v>
+        <v>0.2279246144587377</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2250009707784422</v>
+        <v>0.2226572106661667</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2494626261546647</v>
+        <v>0.2513626261546646</v>
       </c>
       <c r="C98">
-        <v>-271.9805732652237</v>
+        <v>-277.970724841054</v>
       </c>
       <c r="D98">
-        <v>78.7706267347764</v>
+        <v>78.09767515894606</v>
       </c>
       <c r="E98">
-        <v>502.3312</v>
+        <v>507.6484</v>
       </c>
       <c r="F98">
-        <v>510.4512</v>
+        <v>515.7684</v>
       </c>
       <c r="G98">
         <v>159.7</v>
@@ -9323,37 +9323,37 @@
         <v>26.8</v>
       </c>
       <c r="M98">
-        <v>120.36439296</v>
+        <v>121.61818872</v>
       </c>
       <c r="N98">
-        <v>-93.56439296000002</v>
+        <v>-94.81818872000002</v>
       </c>
       <c r="O98">
-        <v>-14.034658944</v>
+        <v>-14.222728308</v>
       </c>
       <c r="P98">
-        <v>-79.52973401600002</v>
+        <v>-80.59546041200002</v>
       </c>
       <c r="Q98">
-        <v>-72.52973401600002</v>
+        <v>-73.59546041200002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7663749068569112</v>
+        <v>1.006566542475882</v>
       </c>
       <c r="T98">
-        <v>13.66903971417426</v>
+        <v>18.22538628556569</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03339858159992501</v>
+        <v>0.03305426632569897</v>
       </c>
       <c r="W98">
-        <v>0.2279246144587377</v>
+        <v>0.2280058040004002</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2226572106661667</v>
+        <v>0.2203617755046599</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2513626261546646</v>
+        <v>0.2532626261546647</v>
       </c>
       <c r="C99">
-        <v>-277.970724841054</v>
+        <v>-283.9494755250049</v>
       </c>
       <c r="D99">
-        <v>78.09767515894606</v>
+        <v>77.43612447499507</v>
       </c>
       <c r="E99">
-        <v>507.6484</v>
+        <v>512.9656</v>
       </c>
       <c r="F99">
-        <v>515.7684</v>
+        <v>521.0856</v>
       </c>
       <c r="G99">
         <v>159.7</v>
@@ -9405,37 +9405,37 @@
         <v>26.8</v>
       </c>
       <c r="M99">
-        <v>121.61818872</v>
+        <v>122.87198448</v>
       </c>
       <c r="N99">
-        <v>-94.81818872000002</v>
+        <v>-96.07198448000001</v>
       </c>
       <c r="O99">
-        <v>-14.222728308</v>
+        <v>-14.410797672</v>
       </c>
       <c r="P99">
-        <v>-80.59546041200002</v>
+        <v>-81.66118680800001</v>
       </c>
       <c r="Q99">
-        <v>-73.59546041200002</v>
+        <v>-74.66118680800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.006566542475882</v>
+        <v>1.486949813713823</v>
       </c>
       <c r="T99">
-        <v>18.22538628556569</v>
+        <v>27.33807942834853</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03305426632569897</v>
+        <v>0.03271697789380409</v>
       </c>
       <c r="W99">
-        <v>0.2280058040004002</v>
+        <v>0.228085336612641</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2203617755046599</v>
+        <v>0.2181131859586939</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2532626261546647</v>
+        <v>0.2551626261546647</v>
       </c>
       <c r="C100">
-        <v>-283.9494755250049</v>
+        <v>-289.9171126079079</v>
       </c>
       <c r="D100">
-        <v>77.43612447499507</v>
+        <v>76.78568739209211</v>
       </c>
       <c r="E100">
-        <v>512.9656</v>
+        <v>518.2828000000001</v>
       </c>
       <c r="F100">
-        <v>521.0856</v>
+        <v>526.4028000000001</v>
       </c>
       <c r="G100">
         <v>159.7</v>
@@ -9487,37 +9487,37 @@
         <v>26.8</v>
       </c>
       <c r="M100">
-        <v>122.87198448</v>
+        <v>124.12578024</v>
       </c>
       <c r="N100">
-        <v>-96.07198448000001</v>
+        <v>-97.32578024000003</v>
       </c>
       <c r="O100">
-        <v>-14.410797672</v>
+        <v>-14.598867036</v>
       </c>
       <c r="P100">
-        <v>-81.66118680800001</v>
+        <v>-82.72691320400003</v>
       </c>
       <c r="Q100">
-        <v>-74.66118680800001</v>
+        <v>-75.72691320400003</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.486949813713823</v>
+        <v>2.928099627427645</v>
       </c>
       <c r="T100">
-        <v>27.33807942834853</v>
+        <v>54.67615885669706</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03271697789380409</v>
+        <v>0.03238650336962424</v>
       </c>
       <c r="W100">
-        <v>0.228085336612641</v>
+        <v>0.2281632625054426</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2181131859586939</v>
+        <v>0.2159100224641617</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2551626261546647</v>
-      </c>
-      <c r="C101">
-        <v>-289.9171126079079</v>
-      </c>
-      <c r="D101">
-        <v>76.78568739209211</v>
-      </c>
-      <c r="E101">
-        <v>518.2828000000001</v>
-      </c>
-      <c r="F101">
-        <v>526.4028000000001</v>
-      </c>
-      <c r="G101">
-        <v>159.7</v>
-      </c>
-      <c r="H101">
-        <v>523.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.8</v>
-      </c>
-      <c r="K101">
-        <v>6.999999999999996</v>
-      </c>
-      <c r="L101">
-        <v>26.8</v>
-      </c>
-      <c r="M101">
-        <v>124.12578024</v>
-      </c>
-      <c r="N101">
-        <v>-97.32578024000003</v>
-      </c>
-      <c r="O101">
-        <v>-14.598867036</v>
-      </c>
-      <c r="P101">
-        <v>-82.72691320400003</v>
-      </c>
-      <c r="Q101">
-        <v>-75.72691320400003</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.928099627427645</v>
-      </c>
-      <c r="T101">
-        <v>54.67615885669706</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03238650336962424</v>
-      </c>
-      <c r="W101">
-        <v>0.2281632625054426</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2159100224641617</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
